--- a/research/traditional_assets/database/data/turkey/turkey_healthcare_products.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_healthcare_products.xlsx
@@ -1525,7 +1525,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1662,22 +1662,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1533567736275854</v>
+        <v>0.1530071316935164</v>
       </c>
       <c r="C2">
-        <v>179.6379656604878</v>
+        <v>178.4063105033678</v>
       </c>
       <c r="D2">
-        <v>172.9779656604878</v>
+        <v>173.5421105033678</v>
       </c>
       <c r="E2">
-        <v>-1.58</v>
+        <v>0.2157999999999998</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.7958</v>
       </c>
       <c r="G2">
         <v>6.66</v>
@@ -1698,28 +1698,28 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.09032874</v>
       </c>
       <c r="N2">
-        <v>7.017499999999999</v>
+        <v>6.927171259999999</v>
       </c>
       <c r="O2">
-        <v>1.754375</v>
+        <v>1.731792815</v>
       </c>
       <c r="P2">
-        <v>5.263125</v>
+        <v>5.195378444999999</v>
       </c>
       <c r="Q2">
-        <v>6.783125</v>
+        <v>6.715378445</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1533567736275854</v>
+        <v>0.1541715976702186</v>
       </c>
       <c r="T2">
-        <v>1.040156204727314</v>
+        <v>1.048036175975249</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>77.68845220247729</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1744,22 +1744,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1530071316935164</v>
+        <v>0.1526574897594475</v>
       </c>
       <c r="C3">
-        <v>178.4063105033678</v>
+        <v>177.1783471547377</v>
       </c>
       <c r="D3">
-        <v>173.5421105033678</v>
+        <v>174.1099471547377</v>
       </c>
       <c r="E3">
-        <v>0.2157999999999998</v>
+        <v>2.0116</v>
       </c>
       <c r="F3">
-        <v>1.7958</v>
+        <v>3.5916</v>
       </c>
       <c r="G3">
         <v>6.66</v>
@@ -1780,28 +1780,28 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M3">
-        <v>0.09032874</v>
+        <v>0.18065748</v>
       </c>
       <c r="N3">
-        <v>6.927171259999999</v>
+        <v>6.836842519999999</v>
       </c>
       <c r="O3">
-        <v>1.731792815</v>
+        <v>1.70921063</v>
       </c>
       <c r="P3">
-        <v>5.195378444999999</v>
+        <v>5.12763189</v>
       </c>
       <c r="Q3">
-        <v>6.715378445</v>
+        <v>6.64763189</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1541715976702186</v>
+        <v>0.1550030507749464</v>
       </c>
       <c r="T3">
-        <v>1.048036175975249</v>
+        <v>1.056076962962937</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>77.68845220247729</v>
+        <v>38.84422610123865</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1826,22 +1826,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1526574897594475</v>
+        <v>0.1523078478253785</v>
       </c>
       <c r="C4">
-        <v>177.1783471547377</v>
+        <v>175.9541119727936</v>
       </c>
       <c r="D4">
-        <v>174.1099471547377</v>
+        <v>174.6815119727936</v>
       </c>
       <c r="E4">
-        <v>2.0116</v>
+        <v>3.8074</v>
       </c>
       <c r="F4">
-        <v>3.5916</v>
+        <v>5.3874</v>
       </c>
       <c r="G4">
         <v>6.66</v>
@@ -1862,28 +1862,28 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M4">
-        <v>0.18065748</v>
+        <v>0.27098622</v>
       </c>
       <c r="N4">
-        <v>6.836842519999999</v>
+        <v>6.746513779999999</v>
       </c>
       <c r="O4">
-        <v>1.70921063</v>
+        <v>1.686628445</v>
       </c>
       <c r="P4">
-        <v>5.12763189</v>
+        <v>5.059885334999999</v>
       </c>
       <c r="Q4">
-        <v>6.64763189</v>
+        <v>6.579885334999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1550030507749464</v>
+        <v>0.1558516472426582</v>
       </c>
       <c r="T4">
-        <v>1.056076962962937</v>
+        <v>1.064283539373051</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>38.84422610123865</v>
+        <v>25.8961507341591</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1908,22 +1908,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1523078478253785</v>
+        <v>0.1519582058913095</v>
       </c>
       <c r="C5">
-        <v>175.9541119727936</v>
+        <v>174.7336417947273</v>
       </c>
       <c r="D5">
-        <v>174.6815119727936</v>
+        <v>175.2568417947273</v>
       </c>
       <c r="E5">
-        <v>3.8074</v>
+        <v>5.6032</v>
       </c>
       <c r="F5">
-        <v>5.3874</v>
+        <v>7.1832</v>
       </c>
       <c r="G5">
         <v>6.66</v>
@@ -1944,28 +1944,28 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M5">
-        <v>0.27098622</v>
+        <v>0.36131496</v>
       </c>
       <c r="N5">
-        <v>6.746513779999999</v>
+        <v>6.65618504</v>
       </c>
       <c r="O5">
-        <v>1.686628445</v>
+        <v>1.66404626</v>
       </c>
       <c r="P5">
-        <v>5.059885334999999</v>
+        <v>4.992138779999999</v>
       </c>
       <c r="Q5">
-        <v>6.579885334999999</v>
+        <v>6.51213878</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1558516472426582</v>
+        <v>0.1567179228034474</v>
       </c>
       <c r="T5">
-        <v>1.064283539373051</v>
+        <v>1.072661086125043</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>25.8961507341591</v>
+        <v>19.42211305061932</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1990,22 +1990,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1519582058913095</v>
+        <v>0.1516085639572406</v>
       </c>
       <c r="C6">
-        <v>174.7336417947273</v>
+        <v>173.5169739446418</v>
       </c>
       <c r="D6">
-        <v>175.2568417947273</v>
+        <v>175.8359739446418</v>
       </c>
       <c r="E6">
-        <v>5.6032</v>
+        <v>7.399000000000001</v>
       </c>
       <c r="F6">
-        <v>7.1832</v>
+        <v>8.979000000000001</v>
       </c>
       <c r="G6">
         <v>6.66</v>
@@ -2026,28 +2026,28 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M6">
-        <v>0.36131496</v>
+        <v>0.4516437</v>
       </c>
       <c r="N6">
-        <v>6.65618504</v>
+        <v>6.565856299999999</v>
       </c>
       <c r="O6">
-        <v>1.66404626</v>
+        <v>1.641464075</v>
       </c>
       <c r="P6">
-        <v>4.992138779999999</v>
+        <v>4.924392224999999</v>
       </c>
       <c r="Q6">
-        <v>6.51213878</v>
+        <v>6.444392225</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1567179228034474</v>
+        <v>0.1576024357444638</v>
       </c>
       <c r="T6">
-        <v>1.072661086125043</v>
+        <v>1.08121500228234</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.42211305061932</v>
+        <v>15.53769044049546</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2072,22 +2072,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1516085639572406</v>
+        <v>0.1512589220231716</v>
       </c>
       <c r="C7">
-        <v>173.5169739446418</v>
+        <v>172.3041462416221</v>
       </c>
       <c r="D7">
-        <v>175.8359739446418</v>
+        <v>176.4189462416221</v>
       </c>
       <c r="E7">
-        <v>7.399000000000001</v>
+        <v>9.194800000000001</v>
       </c>
       <c r="F7">
-        <v>8.979000000000001</v>
+        <v>10.7748</v>
       </c>
       <c r="G7">
         <v>6.66</v>
@@ -2108,28 +2108,28 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M7">
-        <v>0.4516437</v>
+        <v>0.54197244</v>
       </c>
       <c r="N7">
-        <v>6.565856299999999</v>
+        <v>6.475527559999999</v>
       </c>
       <c r="O7">
-        <v>1.641464075</v>
+        <v>1.61888189</v>
       </c>
       <c r="P7">
-        <v>4.924392224999999</v>
+        <v>4.856645669999999</v>
       </c>
       <c r="Q7">
-        <v>6.444392225</v>
+        <v>6.376645669999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1576024357444638</v>
+        <v>0.158505768109757</v>
       </c>
       <c r="T7">
-        <v>1.08121500228234</v>
+        <v>1.08995091665575</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>15.53769044049546</v>
+        <v>12.94807536707955</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2154,22 +2154,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1512589220231716</v>
+        <v>0.1509880300891026</v>
       </c>
       <c r="C8">
-        <v>172.3041462416221</v>
+        <v>170.9626799667932</v>
       </c>
       <c r="D8">
-        <v>176.4189462416221</v>
+        <v>176.8732799667933</v>
       </c>
       <c r="E8">
-        <v>9.194800000000001</v>
+        <v>10.9906</v>
       </c>
       <c r="F8">
-        <v>10.7748</v>
+        <v>12.5706</v>
       </c>
       <c r="G8">
         <v>6.66</v>
@@ -2190,45 +2190,45 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M8">
-        <v>0.54197244</v>
+        <v>0.6511570799999999</v>
       </c>
       <c r="N8">
-        <v>6.475527559999999</v>
+        <v>6.366342919999999</v>
       </c>
       <c r="O8">
-        <v>1.61888189</v>
+        <v>1.59158573</v>
       </c>
       <c r="P8">
-        <v>4.856645669999999</v>
+        <v>4.774757189999999</v>
       </c>
       <c r="Q8">
-        <v>6.376645669999999</v>
+        <v>6.294757189999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.158505768109757</v>
+        <v>0.1594285269775297</v>
       </c>
       <c r="T8">
-        <v>1.08995091665575</v>
+        <v>1.098874700155469</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>12.94807536707955</v>
+        <v>10.77696951402264</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2236,22 +2236,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1509880300891026</v>
+        <v>0.1507516381550337</v>
       </c>
       <c r="C9">
-        <v>170.9626799667932</v>
+        <v>169.5652674285946</v>
       </c>
       <c r="D9">
-        <v>176.8732799667933</v>
+        <v>177.2716674285946</v>
       </c>
       <c r="E9">
-        <v>10.9906</v>
+        <v>12.7864</v>
       </c>
       <c r="F9">
-        <v>12.5706</v>
+        <v>14.3664</v>
       </c>
       <c r="G9">
         <v>6.66</v>
@@ -2272,45 +2272,45 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M9">
-        <v>0.6511570800000002</v>
+        <v>0.7686024</v>
       </c>
       <c r="N9">
-        <v>6.366342919999999</v>
+        <v>6.248897599999999</v>
       </c>
       <c r="O9">
-        <v>1.59158573</v>
+        <v>1.5622244</v>
       </c>
       <c r="P9">
-        <v>4.774757189999999</v>
+        <v>4.6866732</v>
       </c>
       <c r="Q9">
-        <v>6.294757189999999</v>
+        <v>6.2066732</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1594285269775297</v>
+        <v>0.1603713458206888</v>
       </c>
       <c r="T9">
-        <v>1.098874700155469</v>
+        <v>1.107992478948661</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>10.77696951402263</v>
+        <v>9.130208284543476</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2318,22 +2318,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1507516381550337</v>
+        <v>0.1504259962209647</v>
       </c>
       <c r="C10">
-        <v>169.5652674285946</v>
+        <v>168.3212145155724</v>
       </c>
       <c r="D10">
-        <v>177.2716674285946</v>
+        <v>177.8234145155724</v>
       </c>
       <c r="E10">
-        <v>12.7864</v>
+        <v>14.5822</v>
       </c>
       <c r="F10">
-        <v>14.3664</v>
+        <v>16.1622</v>
       </c>
       <c r="G10">
         <v>6.66</v>
@@ -2354,28 +2354,28 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M10">
-        <v>0.7686024</v>
+        <v>0.8646777000000001</v>
       </c>
       <c r="N10">
-        <v>6.248897599999999</v>
+        <v>6.152822299999999</v>
       </c>
       <c r="O10">
-        <v>1.5622244</v>
+        <v>1.538205575</v>
       </c>
       <c r="P10">
-        <v>4.6866732</v>
+        <v>4.614616724999999</v>
       </c>
       <c r="Q10">
-        <v>6.2066732</v>
+        <v>6.134616725</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1603713458206888</v>
+        <v>0.1613348859571041</v>
       </c>
       <c r="T10">
-        <v>1.107992478948661</v>
+        <v>1.11731064848456</v>
       </c>
       <c r="U10">
         <v>0.0535</v>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>9.130208284543476</v>
+        <v>8.115740697371978</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2400,22 +2400,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1504259962209647</v>
+        <v>0.1501603542868958</v>
       </c>
       <c r="C11">
-        <v>168.3212145155724</v>
+        <v>166.9780514970913</v>
       </c>
       <c r="D11">
-        <v>177.8234145155724</v>
+        <v>178.2760514970913</v>
       </c>
       <c r="E11">
-        <v>14.5822</v>
+        <v>16.378</v>
       </c>
       <c r="F11">
-        <v>16.1622</v>
+        <v>17.958</v>
       </c>
       <c r="G11">
         <v>6.66</v>
@@ -2436,45 +2436,45 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M11">
-        <v>0.8646777000000001</v>
+        <v>0.9751194</v>
       </c>
       <c r="N11">
-        <v>6.152822299999999</v>
+        <v>6.0423806</v>
       </c>
       <c r="O11">
-        <v>1.538205575</v>
+        <v>1.51059515</v>
       </c>
       <c r="P11">
-        <v>4.614616724999999</v>
+        <v>4.531785449999999</v>
       </c>
       <c r="Q11">
-        <v>6.134616725</v>
+        <v>6.05178545</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1613348859571041</v>
+        <v>0.1623198380965508</v>
       </c>
       <c r="T11">
-        <v>1.11731064848456</v>
+        <v>1.12683588845459</v>
       </c>
       <c r="U11">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y11">
-        <v>8.115740697371978</v>
+        <v>7.196554596288413</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2482,22 +2482,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1501603542868958</v>
+        <v>0.1498407123528268</v>
       </c>
       <c r="C12">
-        <v>166.9780514970913</v>
+        <v>165.7299649893391</v>
       </c>
       <c r="D12">
-        <v>178.2760514970913</v>
+        <v>178.8237649893391</v>
       </c>
       <c r="E12">
-        <v>16.378</v>
+        <v>18.1738</v>
       </c>
       <c r="F12">
-        <v>17.958</v>
+        <v>19.7538</v>
       </c>
       <c r="G12">
         <v>6.66</v>
@@ -2518,28 +2518,28 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M12">
-        <v>0.9751194000000001</v>
+        <v>1.07263134</v>
       </c>
       <c r="N12">
-        <v>6.0423806</v>
+        <v>5.944868659999999</v>
       </c>
       <c r="O12">
-        <v>1.51059515</v>
+        <v>1.486217165</v>
       </c>
       <c r="P12">
-        <v>4.531785449999999</v>
+        <v>4.458651495</v>
       </c>
       <c r="Q12">
-        <v>6.05178545</v>
+        <v>5.978651495</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1623198380965508</v>
+        <v>0.1633269239919402</v>
       </c>
       <c r="T12">
-        <v>1.12683588845459</v>
+        <v>1.136575178761026</v>
       </c>
       <c r="U12">
         <v>0.0543</v>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.196554596288412</v>
+        <v>6.542322360262193</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2564,22 +2564,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1498407123528268</v>
+        <v>0.1496110704187578</v>
       </c>
       <c r="C13">
-        <v>165.7299649893391</v>
+        <v>164.3297435638013</v>
       </c>
       <c r="D13">
-        <v>178.8237649893391</v>
+        <v>179.2193435638013</v>
       </c>
       <c r="E13">
-        <v>18.1738</v>
+        <v>19.9696</v>
       </c>
       <c r="F13">
-        <v>19.7538</v>
+        <v>21.5496</v>
       </c>
       <c r="G13">
         <v>6.66</v>
@@ -2600,45 +2600,45 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M13">
-        <v>1.07263134</v>
+        <v>1.19169288</v>
       </c>
       <c r="N13">
-        <v>5.944868659999999</v>
+        <v>5.825807119999999</v>
       </c>
       <c r="O13">
-        <v>1.486217165</v>
+        <v>1.45645178</v>
       </c>
       <c r="P13">
-        <v>4.458651495</v>
+        <v>4.369355339999998</v>
       </c>
       <c r="Q13">
-        <v>5.978651495</v>
+        <v>5.889355339999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1633269239919402</v>
+        <v>0.1643568982031339</v>
       </c>
       <c r="T13">
-        <v>1.136575178761026</v>
+        <v>1.146535816574426</v>
       </c>
       <c r="U13">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y13">
-        <v>6.542322360262193</v>
+        <v>5.888681654286629</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2646,22 +2646,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1496110704187578</v>
+        <v>0.1492989284846889</v>
       </c>
       <c r="C14">
-        <v>164.3297435638013</v>
+        <v>163.0744503433555</v>
       </c>
       <c r="D14">
-        <v>179.2193435638013</v>
+        <v>179.7598503433555</v>
       </c>
       <c r="E14">
-        <v>19.9696</v>
+        <v>21.7654</v>
       </c>
       <c r="F14">
-        <v>21.5496</v>
+        <v>23.3454</v>
       </c>
       <c r="G14">
         <v>6.66</v>
@@ -2682,28 +2682,28 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M14">
-        <v>1.19169288</v>
+        <v>1.29100062</v>
       </c>
       <c r="N14">
-        <v>5.825807119999999</v>
+        <v>5.726499379999999</v>
       </c>
       <c r="O14">
-        <v>1.45645178</v>
+        <v>1.431624845</v>
       </c>
       <c r="P14">
-        <v>4.369355339999998</v>
+        <v>4.294874534999999</v>
       </c>
       <c r="Q14">
-        <v>5.889355339999999</v>
+        <v>5.814874535</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1643568982031339</v>
+        <v>0.165410549982401</v>
       </c>
       <c r="T14">
-        <v>1.146535816574426</v>
+        <v>1.156725434567444</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.888681654286629</v>
+        <v>5.435706142418428</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2728,22 +2728,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1492989284846889</v>
+        <v>0.1489867865506199</v>
       </c>
       <c r="C15">
-        <v>163.0744503433555</v>
+        <v>161.8224272088808</v>
       </c>
       <c r="D15">
-        <v>179.7598503433555</v>
+        <v>180.3036272088808</v>
       </c>
       <c r="E15">
-        <v>21.7654</v>
+        <v>23.5612</v>
       </c>
       <c r="F15">
-        <v>23.3454</v>
+        <v>25.1412</v>
       </c>
       <c r="G15">
         <v>6.66</v>
@@ -2764,28 +2764,28 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M15">
-        <v>1.29100062</v>
+        <v>1.39030836</v>
       </c>
       <c r="N15">
-        <v>5.726499379999999</v>
+        <v>5.627191639999999</v>
       </c>
       <c r="O15">
-        <v>1.431624845</v>
+        <v>1.40679791</v>
       </c>
       <c r="P15">
-        <v>4.294874534999999</v>
+        <v>4.220393729999999</v>
       </c>
       <c r="Q15">
-        <v>5.814874535</v>
+        <v>5.740393729999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.165410549982401</v>
+        <v>0.1664887052914185</v>
       </c>
       <c r="T15">
-        <v>1.156725434567444</v>
+        <v>1.167152020420765</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.435706142418428</v>
+        <v>5.047441417959968</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2810,22 +2810,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1489867865506199</v>
+        <v>0.1486746446165509</v>
       </c>
       <c r="C16">
-        <v>161.8224272088808</v>
+        <v>160.5737039266319</v>
       </c>
       <c r="D16">
-        <v>180.3036272088808</v>
+        <v>180.8507039266319</v>
       </c>
       <c r="E16">
-        <v>23.5612</v>
+        <v>25.357</v>
       </c>
       <c r="F16">
-        <v>25.1412</v>
+        <v>26.937</v>
       </c>
       <c r="G16">
         <v>6.66</v>
@@ -2846,28 +2846,28 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M16">
-        <v>1.39030836</v>
+        <v>1.4896161</v>
       </c>
       <c r="N16">
-        <v>5.627191639999999</v>
+        <v>5.527883899999999</v>
       </c>
       <c r="O16">
-        <v>1.40679791</v>
+        <v>1.381970975</v>
       </c>
       <c r="P16">
-        <v>4.220393729999999</v>
+        <v>4.145912924999999</v>
       </c>
       <c r="Q16">
-        <v>5.740393729999999</v>
+        <v>5.665912925</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1664887052914185</v>
+        <v>0.1675922289606482</v>
       </c>
       <c r="T16">
-        <v>1.167152020420765</v>
+        <v>1.177823937705929</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.047441417959968</v>
+        <v>4.710945323429303</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2892,22 +2892,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1486746446165509</v>
+        <v>0.148662502682482</v>
       </c>
       <c r="C17">
-        <v>160.5737039266319</v>
+        <v>158.7992516215269</v>
       </c>
       <c r="D17">
-        <v>180.8507039266319</v>
+        <v>180.8720516215269</v>
       </c>
       <c r="E17">
-        <v>25.357</v>
+        <v>27.1528</v>
       </c>
       <c r="F17">
-        <v>26.937</v>
+        <v>28.7328</v>
       </c>
       <c r="G17">
         <v>6.66</v>
@@ -2928,45 +2928,45 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M17">
-        <v>1.4896161</v>
+        <v>1.66075584</v>
       </c>
       <c r="N17">
-        <v>5.527883899999999</v>
+        <v>5.356744159999999</v>
       </c>
       <c r="O17">
-        <v>1.381970975</v>
+        <v>1.33918604</v>
       </c>
       <c r="P17">
-        <v>4.145912924999999</v>
+        <v>4.017558119999999</v>
       </c>
       <c r="Q17">
-        <v>5.665912925</v>
+        <v>5.53755812</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1675922289606482</v>
+        <v>0.1687220270029547</v>
       </c>
       <c r="T17">
-        <v>1.177823937705929</v>
+        <v>1.188749948259788</v>
       </c>
       <c r="U17">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.710945323429303</v>
+        <v>4.225485668019688</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2974,22 +2974,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.148662502682482</v>
+        <v>0.148815360748413</v>
       </c>
       <c r="C18">
-        <v>158.7992516215269</v>
+        <v>156.7350668700589</v>
       </c>
       <c r="D18">
-        <v>180.8720516215269</v>
+        <v>180.6036668700589</v>
       </c>
       <c r="E18">
-        <v>27.1528</v>
+        <v>28.9486</v>
       </c>
       <c r="F18">
-        <v>28.7328</v>
+        <v>30.5286</v>
       </c>
       <c r="G18">
         <v>6.66</v>
@@ -3010,45 +3010,45 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M18">
-        <v>1.66075584</v>
+        <v>1.87140318</v>
       </c>
       <c r="N18">
-        <v>5.356744159999999</v>
+        <v>5.146096819999999</v>
       </c>
       <c r="O18">
-        <v>1.33918604</v>
+        <v>1.286524205</v>
       </c>
       <c r="P18">
-        <v>4.017558119999999</v>
+        <v>3.859572614999999</v>
       </c>
       <c r="Q18">
-        <v>5.53755812</v>
+        <v>5.379572614999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1687220270029547</v>
+        <v>0.1698790490944735</v>
       </c>
       <c r="T18">
-        <v>1.188749948259788</v>
+        <v>1.19993923617639</v>
       </c>
       <c r="U18">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.225485668019688</v>
+        <v>3.749860038177341</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3056,22 +3056,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.148815360748413</v>
+        <v>0.148548218814344</v>
       </c>
       <c r="C19">
-        <v>156.7350668700589</v>
+        <v>155.4088303663838</v>
       </c>
       <c r="D19">
-        <v>180.6036668700589</v>
+        <v>181.0732303663838</v>
       </c>
       <c r="E19">
-        <v>28.9486</v>
+        <v>30.7444</v>
       </c>
       <c r="F19">
-        <v>30.5286</v>
+        <v>32.3244</v>
       </c>
       <c r="G19">
         <v>6.66</v>
@@ -3092,28 +3092,28 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M19">
-        <v>1.87140318</v>
+        <v>1.98148572</v>
       </c>
       <c r="N19">
-        <v>5.146096819999999</v>
+        <v>5.036014279999999</v>
       </c>
       <c r="O19">
-        <v>1.286524205</v>
+        <v>1.25900357</v>
       </c>
       <c r="P19">
-        <v>3.859572614999999</v>
+        <v>3.777010709999999</v>
       </c>
       <c r="Q19">
-        <v>5.379572614999999</v>
+        <v>5.297010709999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1698790490944735</v>
+        <v>0.1710642912370049</v>
       </c>
       <c r="T19">
-        <v>1.19993923617639</v>
+        <v>1.211401433554372</v>
       </c>
       <c r="U19">
         <v>0.0613</v>
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.749860038177341</v>
+        <v>3.541534480500823</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3138,22 +3138,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.148548218814344</v>
+        <v>0.1486800768802751</v>
       </c>
       <c r="C20">
-        <v>155.4088303663838</v>
+        <v>153.3809546655094</v>
       </c>
       <c r="D20">
-        <v>181.0732303663838</v>
+        <v>180.8411546655094</v>
       </c>
       <c r="E20">
-        <v>30.7444</v>
+        <v>32.54020000000001</v>
       </c>
       <c r="F20">
-        <v>32.3244</v>
+        <v>34.1202</v>
       </c>
       <c r="G20">
         <v>6.66</v>
@@ -3174,45 +3174,45 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M20">
-        <v>1.98148572</v>
+        <v>2.187104820000001</v>
       </c>
       <c r="N20">
-        <v>5.036014279999999</v>
+        <v>4.830395179999998</v>
       </c>
       <c r="O20">
-        <v>1.25900357</v>
+        <v>1.207598795</v>
       </c>
       <c r="P20">
-        <v>3.777010709999999</v>
+        <v>3.622796384999999</v>
       </c>
       <c r="Q20">
-        <v>5.297010709999999</v>
+        <v>5.142796384999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1710642912370049</v>
+        <v>0.1722787986176235</v>
       </c>
       <c r="T20">
-        <v>1.211401433554372</v>
+        <v>1.223146648151564</v>
       </c>
       <c r="U20">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.541534480500823</v>
+        <v>3.208579641829877</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3220,22 +3220,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1486800768802751</v>
+        <v>0.1484339349462061</v>
       </c>
       <c r="C21">
-        <v>153.3809546655094</v>
+        <v>152.0188571401536</v>
       </c>
       <c r="D21">
-        <v>180.8411546655094</v>
+        <v>181.2748571401536</v>
       </c>
       <c r="E21">
-        <v>32.54020000000001</v>
+        <v>34.33600000000001</v>
       </c>
       <c r="F21">
-        <v>34.1202</v>
+        <v>35.916</v>
       </c>
       <c r="G21">
         <v>6.66</v>
@@ -3256,28 +3256,28 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M21">
-        <v>2.187104820000001</v>
+        <v>2.3022156</v>
       </c>
       <c r="N21">
-        <v>4.830395179999998</v>
+        <v>4.715284399999999</v>
       </c>
       <c r="O21">
-        <v>1.207598795</v>
+        <v>1.1788211</v>
       </c>
       <c r="P21">
-        <v>3.622796384999999</v>
+        <v>3.536463299999999</v>
       </c>
       <c r="Q21">
-        <v>5.142796384999999</v>
+        <v>5.0564633</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1722787986176235</v>
+        <v>0.1735236686827576</v>
       </c>
       <c r="T21">
-        <v>1.223146648151564</v>
+        <v>1.235185493113686</v>
       </c>
       <c r="U21">
         <v>0.0641</v>
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.208579641829877</v>
+        <v>3.048150659738384</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3302,22 +3302,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1484339349462061</v>
+        <v>0.1494162930121372</v>
       </c>
       <c r="C22">
-        <v>152.0188571401536</v>
+        <v>148.5044392193091</v>
       </c>
       <c r="D22">
-        <v>181.2748571401536</v>
+        <v>179.5562392193091</v>
       </c>
       <c r="E22">
-        <v>34.33600000000001</v>
+        <v>36.13180000000001</v>
       </c>
       <c r="F22">
-        <v>35.916</v>
+        <v>37.7118</v>
       </c>
       <c r="G22">
         <v>6.66</v>
@@ -3338,45 +3338,45 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M22">
-        <v>2.3022156</v>
+        <v>2.711478420000001</v>
       </c>
       <c r="N22">
-        <v>4.715284399999999</v>
+        <v>4.306021579999999</v>
       </c>
       <c r="O22">
-        <v>1.1788211</v>
+        <v>1.076505395</v>
       </c>
       <c r="P22">
-        <v>3.536463299999999</v>
+        <v>3.229516184999999</v>
       </c>
       <c r="Q22">
-        <v>5.0564633</v>
+        <v>4.749516184999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1735236686827576</v>
+        <v>0.1748000544457432</v>
       </c>
       <c r="T22">
-        <v>1.235185493113686</v>
+        <v>1.247529118960924</v>
       </c>
       <c r="U22">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.048150659738384</v>
+        <v>2.588071492009145</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3384,22 +3384,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1494162930121372</v>
+        <v>0.1498721510780682</v>
       </c>
       <c r="C23">
-        <v>148.5044392193091</v>
+        <v>145.9221448585367</v>
       </c>
       <c r="D23">
-        <v>179.5562392193091</v>
+        <v>178.7697448585367</v>
       </c>
       <c r="E23">
-        <v>36.13180000000001</v>
+        <v>37.92760000000001</v>
       </c>
       <c r="F23">
-        <v>37.7118</v>
+        <v>39.5076</v>
       </c>
       <c r="G23">
         <v>6.66</v>
@@ -3420,45 +3420,45 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M23">
-        <v>2.711478420000001</v>
+        <v>2.994676080000001</v>
       </c>
       <c r="N23">
-        <v>4.306021579999999</v>
+        <v>4.022823919999999</v>
       </c>
       <c r="O23">
-        <v>1.076505395</v>
+        <v>1.00570598</v>
       </c>
       <c r="P23">
-        <v>3.229516184999999</v>
+        <v>3.017117939999999</v>
       </c>
       <c r="Q23">
-        <v>4.749516184999999</v>
+        <v>4.53711794</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1748000544457432</v>
+        <v>0.1761091680488054</v>
       </c>
       <c r="T23">
-        <v>1.247529118960924</v>
+        <v>1.260189248035015</v>
       </c>
       <c r="U23">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y23">
-        <v>2.588071492009145</v>
+        <v>2.343325225344572</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3466,22 +3466,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1498721510780682</v>
+        <v>0.1497137591439992</v>
       </c>
       <c r="C24">
-        <v>145.9221448585367</v>
+        <v>144.3988370277586</v>
       </c>
       <c r="D24">
-        <v>178.7697448585367</v>
+        <v>179.0422370277586</v>
       </c>
       <c r="E24">
-        <v>37.92760000000001</v>
+        <v>39.72340000000001</v>
       </c>
       <c r="F24">
-        <v>39.5076</v>
+        <v>41.3034</v>
       </c>
       <c r="G24">
         <v>6.66</v>
@@ -3502,28 +3502,28 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M24">
-        <v>2.994676080000001</v>
+        <v>3.13079772</v>
       </c>
       <c r="N24">
-        <v>4.022823919999999</v>
+        <v>3.886702279999999</v>
       </c>
       <c r="O24">
-        <v>1.00570598</v>
+        <v>0.9716755699999997</v>
       </c>
       <c r="P24">
-        <v>3.017117939999999</v>
+        <v>2.915026709999999</v>
       </c>
       <c r="Q24">
-        <v>4.53711794</v>
+        <v>4.43502671</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1761091680488054</v>
+        <v>0.1774522846025964</v>
       </c>
       <c r="T24">
-        <v>1.260189248035015</v>
+        <v>1.273178211630511</v>
       </c>
       <c r="U24">
         <v>0.07580000000000001</v>
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.343325225344572</v>
+        <v>2.241441519894808</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3548,22 +3548,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1497137591439992</v>
+        <v>0.1495553672099303</v>
       </c>
       <c r="C25">
-        <v>144.3988370277586</v>
+        <v>142.8763611647691</v>
       </c>
       <c r="D25">
-        <v>179.0422370277586</v>
+        <v>179.3155611647691</v>
       </c>
       <c r="E25">
-        <v>39.72340000000001</v>
+        <v>41.5192</v>
       </c>
       <c r="F25">
-        <v>41.3034</v>
+        <v>43.0992</v>
       </c>
       <c r="G25">
         <v>6.66</v>
@@ -3584,28 +3584,28 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M25">
-        <v>3.13079772</v>
+        <v>3.266919360000001</v>
       </c>
       <c r="N25">
-        <v>3.886702279999999</v>
+        <v>3.750580639999999</v>
       </c>
       <c r="O25">
-        <v>0.9716755699999997</v>
+        <v>0.9376451599999996</v>
       </c>
       <c r="P25">
-        <v>2.915026709999999</v>
+        <v>2.812935479999999</v>
       </c>
       <c r="Q25">
-        <v>4.43502671</v>
+        <v>4.33293548</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1774522846025964</v>
+        <v>0.1788307463288556</v>
       </c>
       <c r="T25">
-        <v>1.273178211630511</v>
+        <v>1.286508990057468</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.241441519894808</v>
+        <v>2.148048123232524</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3630,22 +3630,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1495553672099303</v>
+        <v>0.1493969752758613</v>
       </c>
       <c r="C26">
-        <v>142.8763611647691</v>
+        <v>141.3547210856154</v>
       </c>
       <c r="D26">
-        <v>179.3155611647691</v>
+        <v>179.5897210856154</v>
       </c>
       <c r="E26">
-        <v>41.5192</v>
+        <v>43.315</v>
       </c>
       <c r="F26">
-        <v>43.0992</v>
+        <v>44.895</v>
       </c>
       <c r="G26">
         <v>6.66</v>
@@ -3666,28 +3666,28 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M26">
-        <v>3.266919360000001</v>
+        <v>3.403041</v>
       </c>
       <c r="N26">
-        <v>3.750580639999999</v>
+        <v>3.614458999999999</v>
       </c>
       <c r="O26">
-        <v>0.9376451599999996</v>
+        <v>0.9036147499999997</v>
       </c>
       <c r="P26">
-        <v>2.812935479999999</v>
+        <v>2.710844249999999</v>
       </c>
       <c r="Q26">
-        <v>4.33293548</v>
+        <v>4.23084425</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1788307463288556</v>
+        <v>0.1802459670344817</v>
       </c>
       <c r="T26">
-        <v>1.286508990057468</v>
+        <v>1.300195255909143</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.148048123232524</v>
+        <v>2.062126198303223</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3712,22 +3712,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1493969752758613</v>
+        <v>0.1520075833417923</v>
       </c>
       <c r="C27">
-        <v>141.3547210856154</v>
+        <v>135.1445623395396</v>
       </c>
       <c r="D27">
-        <v>179.5897210856154</v>
+        <v>175.1753623395396</v>
       </c>
       <c r="E27">
-        <v>43.315</v>
+        <v>45.1108</v>
       </c>
       <c r="F27">
-        <v>44.895</v>
+        <v>46.6908</v>
       </c>
       <c r="G27">
         <v>6.66</v>
@@ -3748,45 +3748,45 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M27">
-        <v>3.403041</v>
+        <v>4.202172</v>
       </c>
       <c r="N27">
-        <v>3.614458999999999</v>
+        <v>2.815327999999999</v>
       </c>
       <c r="O27">
-        <v>0.9036147499999997</v>
+        <v>0.7038319999999998</v>
       </c>
       <c r="P27">
-        <v>2.710844249999999</v>
+        <v>2.111495999999999</v>
       </c>
       <c r="Q27">
-        <v>4.23084425</v>
+        <v>3.631496</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1802459670344817</v>
+        <v>0.181699436948368</v>
       </c>
       <c r="T27">
-        <v>1.300195255909143</v>
+        <v>1.31425142083789</v>
       </c>
       <c r="U27">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.062126198303223</v>
+        <v>1.669969720420773</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3794,22 +3794,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1520075833417923</v>
+        <v>0.1519556914077234</v>
       </c>
       <c r="C28">
-        <v>135.1445623395396</v>
+        <v>133.4343930601584</v>
       </c>
       <c r="D28">
-        <v>175.1753623395396</v>
+        <v>175.2609930601585</v>
       </c>
       <c r="E28">
-        <v>45.1108</v>
+        <v>46.90660000000001</v>
       </c>
       <c r="F28">
-        <v>46.6908</v>
+        <v>48.48660000000001</v>
       </c>
       <c r="G28">
         <v>6.66</v>
@@ -3830,28 +3830,28 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M28">
-        <v>4.202172</v>
+        <v>4.363794</v>
       </c>
       <c r="N28">
-        <v>2.815327999999999</v>
+        <v>2.653705999999999</v>
       </c>
       <c r="O28">
-        <v>0.7038319999999998</v>
+        <v>0.6634264999999997</v>
       </c>
       <c r="P28">
-        <v>2.111495999999999</v>
+        <v>1.990279499999999</v>
       </c>
       <c r="Q28">
-        <v>3.631496</v>
+        <v>3.510279499999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.181699436948368</v>
+        <v>0.1831927279557855</v>
       </c>
       <c r="T28">
-        <v>1.31425142083789</v>
+        <v>1.328692686175645</v>
       </c>
       <c r="U28">
         <v>0.09</v>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>1.669969720420773</v>
+        <v>1.608118990034818</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3876,22 +3876,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1519556914077234</v>
+        <v>0.1519037994736544</v>
       </c>
       <c r="C29">
-        <v>133.4343930601584</v>
+        <v>131.7243075392049</v>
       </c>
       <c r="D29">
-        <v>175.2609930601585</v>
+        <v>175.3467075392049</v>
       </c>
       <c r="E29">
-        <v>46.90660000000001</v>
+        <v>48.70240000000001</v>
       </c>
       <c r="F29">
-        <v>48.48660000000001</v>
+        <v>50.28240000000001</v>
       </c>
       <c r="G29">
         <v>6.66</v>
@@ -3912,28 +3912,28 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M29">
-        <v>4.363794</v>
+        <v>4.525416000000001</v>
       </c>
       <c r="N29">
-        <v>2.653705999999999</v>
+        <v>2.492083999999998</v>
       </c>
       <c r="O29">
-        <v>0.6634264999999997</v>
+        <v>0.6230209999999996</v>
       </c>
       <c r="P29">
-        <v>1.990279499999999</v>
+        <v>1.869062999999999</v>
       </c>
       <c r="Q29">
-        <v>3.510279499999999</v>
+        <v>3.389062999999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1831927279557855</v>
+        <v>0.1847274992689645</v>
       </c>
       <c r="T29">
-        <v>1.328692686175645</v>
+        <v>1.343535097772781</v>
       </c>
       <c r="U29">
         <v>0.09</v>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.608118990034818</v>
+        <v>1.550686168962146</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3958,22 +3958,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1519037994736544</v>
+        <v>0.1657197065681124</v>
       </c>
       <c r="C30">
-        <v>131.7243075392049</v>
+        <v>109.7268752136223</v>
       </c>
       <c r="D30">
-        <v>175.3467075392049</v>
+        <v>155.1450752136224</v>
       </c>
       <c r="E30">
-        <v>48.70240000000001</v>
+        <v>50.49820000000001</v>
       </c>
       <c r="F30">
-        <v>50.28240000000001</v>
+        <v>52.07820000000001</v>
       </c>
       <c r="G30">
         <v>6.66</v>
@@ -3994,45 +3994,45 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M30">
-        <v>4.525416000000001</v>
+        <v>7.645079760000002</v>
       </c>
       <c r="N30">
-        <v>2.492083999999998</v>
+        <v>-0.6275797600000033</v>
       </c>
       <c r="O30">
-        <v>0.6230209999999996</v>
+        <v>-0.1568949400000008</v>
       </c>
       <c r="P30">
-        <v>1.869062999999999</v>
+        <v>-0.4706848200000024</v>
       </c>
       <c r="Q30">
-        <v>3.389062999999999</v>
+        <v>1.049315179999998</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1847274992689645</v>
+        <v>0.1872070837078506</v>
       </c>
       <c r="T30">
-        <v>1.343535097772781</v>
+        <v>1.367514574399544</v>
       </c>
       <c r="U30">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V30">
-        <v>0.25</v>
+        <v>0.2294776581899257</v>
       </c>
       <c r="W30">
-        <v>0.0675</v>
+        <v>0.1131126797777189</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y30">
-        <v>1.550686168962146</v>
+        <v>0.9179106327597029</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4040,22 +4040,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1657197065681124</v>
+        <v>0.1667297065681124</v>
       </c>
       <c r="C31">
-        <v>109.7268752136224</v>
+        <v>106.6353098437006</v>
       </c>
       <c r="D31">
-        <v>155.1450752136224</v>
+        <v>153.8493098437006</v>
       </c>
       <c r="E31">
-        <v>50.4982</v>
+        <v>52.294</v>
       </c>
       <c r="F31">
-        <v>52.0782</v>
+        <v>53.874</v>
       </c>
       <c r="G31">
         <v>6.66</v>
@@ -4076,37 +4076,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M31">
-        <v>7.645079760000001</v>
+        <v>7.908703200000001</v>
       </c>
       <c r="N31">
-        <v>-0.6275797600000015</v>
+        <v>-0.8912032000000023</v>
       </c>
       <c r="O31">
-        <v>-0.1568949400000004</v>
+        <v>-0.2228008000000006</v>
       </c>
       <c r="P31">
-        <v>-0.4706848200000011</v>
+        <v>-0.6684024000000017</v>
       </c>
       <c r="Q31">
-        <v>1.049315179999999</v>
+        <v>0.8515975999999987</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1872070837078506</v>
+        <v>0.189227184903677</v>
       </c>
       <c r="T31">
-        <v>1.367514574399544</v>
+        <v>1.387050496890966</v>
       </c>
       <c r="U31">
         <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.2294776581899258</v>
+        <v>0.2218284029169282</v>
       </c>
       <c r="W31">
-        <v>0.1131126797777189</v>
+        <v>0.114235590451795</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.9179106327597031</v>
+        <v>0.8873136116677128</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4122,22 +4122,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1667297065681124</v>
+        <v>0.1677397065681124</v>
       </c>
       <c r="C32">
-        <v>106.6353098437006</v>
+        <v>103.565209557802</v>
       </c>
       <c r="D32">
-        <v>153.8493098437006</v>
+        <v>152.575009557802</v>
       </c>
       <c r="E32">
-        <v>52.294</v>
+        <v>54.0898</v>
       </c>
       <c r="F32">
-        <v>53.874</v>
+        <v>55.6698</v>
       </c>
       <c r="G32">
         <v>6.66</v>
@@ -4158,37 +4158,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M32">
-        <v>7.908703200000001</v>
+        <v>8.172326640000001</v>
       </c>
       <c r="N32">
-        <v>-0.8912032000000023</v>
+        <v>-1.154826640000002</v>
       </c>
       <c r="O32">
-        <v>-0.2228008000000006</v>
+        <v>-0.2887066600000006</v>
       </c>
       <c r="P32">
-        <v>-0.6684024000000017</v>
+        <v>-0.8661199800000017</v>
       </c>
       <c r="Q32">
-        <v>0.8515975999999987</v>
+        <v>0.6538800199999988</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.189227184903677</v>
+        <v>0.1913058397573535</v>
       </c>
       <c r="T32">
-        <v>1.387050496890966</v>
+        <v>1.407152678005328</v>
       </c>
       <c r="U32">
         <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.2218284029169282</v>
+        <v>0.2146726479841241</v>
       </c>
       <c r="W32">
-        <v>0.114235590451795</v>
+        <v>0.1152860552759306</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.8873136116677128</v>
+        <v>0.8586905919364963</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4204,22 +4204,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1677397065681124</v>
+        <v>0.1687497065681124</v>
       </c>
       <c r="C33">
-        <v>103.565209557802</v>
+        <v>100.5160453656068</v>
       </c>
       <c r="D33">
-        <v>152.575009557802</v>
+        <v>151.3216453656068</v>
       </c>
       <c r="E33">
-        <v>54.0898</v>
+        <v>55.8856</v>
       </c>
       <c r="F33">
-        <v>55.6698</v>
+        <v>57.4656</v>
       </c>
       <c r="G33">
         <v>6.66</v>
@@ -4240,37 +4240,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M33">
-        <v>8.172326640000001</v>
+        <v>8.435950080000001</v>
       </c>
       <c r="N33">
-        <v>-1.154826640000002</v>
+        <v>-1.418450080000002</v>
       </c>
       <c r="O33">
-        <v>-0.2887066600000006</v>
+        <v>-0.3546125200000005</v>
       </c>
       <c r="P33">
-        <v>-0.8661199800000017</v>
+        <v>-1.063837560000002</v>
       </c>
       <c r="Q33">
-        <v>0.6538800199999988</v>
+        <v>0.4561624399999988</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1913058397573535</v>
+        <v>0.1934456315184911</v>
       </c>
       <c r="T33">
-        <v>1.407152678005328</v>
+        <v>1.4278460997407</v>
       </c>
       <c r="U33">
         <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.2146726479841241</v>
+        <v>0.2079641277346202</v>
       </c>
       <c r="W33">
-        <v>0.1152860552759306</v>
+        <v>0.1162708660485578</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8586905919364963</v>
+        <v>0.8318565109384808</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4286,22 +4286,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1687497065681124</v>
+        <v>0.1697597065681124</v>
       </c>
       <c r="C34">
-        <v>100.5160453656068</v>
+        <v>97.48730551724339</v>
       </c>
       <c r="D34">
-        <v>151.3216453656068</v>
+        <v>150.0887055172434</v>
       </c>
       <c r="E34">
-        <v>55.8856</v>
+        <v>57.68140000000001</v>
       </c>
       <c r="F34">
-        <v>57.4656</v>
+        <v>59.26140000000001</v>
       </c>
       <c r="G34">
         <v>6.66</v>
@@ -4322,37 +4322,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M34">
-        <v>8.435950080000001</v>
+        <v>8.699573520000001</v>
       </c>
       <c r="N34">
-        <v>-1.418450080000002</v>
+        <v>-1.682073520000002</v>
       </c>
       <c r="O34">
-        <v>-0.3546125200000005</v>
+        <v>-0.4205183800000005</v>
       </c>
       <c r="P34">
-        <v>-1.063837560000002</v>
+        <v>-1.261555140000002</v>
       </c>
       <c r="Q34">
-        <v>0.4561624399999988</v>
+        <v>0.2584448599999989</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1934456315184911</v>
+        <v>0.1956492976605581</v>
       </c>
       <c r="T34">
-        <v>1.4278460997407</v>
+        <v>1.449157235557726</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.2079641277346202</v>
+        <v>0.2016621844699348</v>
       </c>
       <c r="W34">
-        <v>0.1162708660485578</v>
+        <v>0.1171959913198136</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8318565109384808</v>
+        <v>0.806648737879739</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4368,22 +4368,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1697597065681124</v>
+        <v>0.1910545979352968</v>
       </c>
       <c r="C35">
-        <v>97.48730551724339</v>
+        <v>73.68791509833817</v>
       </c>
       <c r="D35">
-        <v>150.0887055172434</v>
+        <v>128.0851150983382</v>
       </c>
       <c r="E35">
-        <v>57.68140000000001</v>
+        <v>59.47720000000001</v>
       </c>
       <c r="F35">
-        <v>59.26140000000001</v>
+        <v>61.05720000000001</v>
       </c>
       <c r="G35">
         <v>6.66</v>
@@ -4404,45 +4404,45 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M35">
-        <v>8.699573520000001</v>
+        <v>12.26028576</v>
       </c>
       <c r="N35">
-        <v>-1.682073520000002</v>
+        <v>-5.242785760000003</v>
       </c>
       <c r="O35">
-        <v>-0.4205183800000005</v>
+        <v>-1.310696440000001</v>
       </c>
       <c r="P35">
-        <v>-1.261555140000002</v>
+        <v>-3.932089320000002</v>
       </c>
       <c r="Q35">
-        <v>0.2584448599999989</v>
+        <v>-2.412089320000002</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1956492976605581</v>
+        <v>0.2008362436359974</v>
       </c>
       <c r="T35">
-        <v>1.449157235557726</v>
+        <v>1.499318967431718</v>
       </c>
       <c r="U35">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.2016621844699348</v>
+        <v>0.1430941361679974</v>
       </c>
       <c r="W35">
-        <v>0.1171959913198136</v>
+        <v>0.1720666974574661</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.806648737879739</v>
+        <v>0.5723765446719896</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4450,22 +4450,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1910545979352968</v>
+        <v>0.1926045979352967</v>
       </c>
       <c r="C36">
-        <v>73.68791509833817</v>
+        <v>70.53976012312194</v>
       </c>
       <c r="D36">
-        <v>128.0851150983382</v>
+        <v>126.7327601231219</v>
       </c>
       <c r="E36">
-        <v>59.47720000000001</v>
+        <v>61.27300000000001</v>
       </c>
       <c r="F36">
-        <v>61.05720000000001</v>
+        <v>62.85300000000001</v>
       </c>
       <c r="G36">
         <v>6.66</v>
@@ -4486,37 +4486,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M36">
-        <v>12.26028576</v>
+        <v>12.6208824</v>
       </c>
       <c r="N36">
-        <v>-5.242785760000003</v>
+        <v>-5.603382400000004</v>
       </c>
       <c r="O36">
-        <v>-1.310696440000001</v>
+        <v>-1.400845600000001</v>
       </c>
       <c r="P36">
-        <v>-3.932089320000002</v>
+        <v>-4.202536800000003</v>
       </c>
       <c r="Q36">
-        <v>-2.412089320000002</v>
+        <v>-2.682536800000002</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2008362436359974</v>
+        <v>0.2032214166150128</v>
       </c>
       <c r="T36">
-        <v>1.499318967431718</v>
+        <v>1.522385413084513</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.1430941361679974</v>
+        <v>0.1390057322774832</v>
       </c>
       <c r="W36">
-        <v>0.1720666974574661</v>
+        <v>0.1728876489586814</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.5723765446719896</v>
+        <v>0.5560229291099328</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4532,22 +4532,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1926045979352967</v>
+        <v>0.1941545979352967</v>
       </c>
       <c r="C37">
-        <v>70.53976012312194</v>
+        <v>67.41986379631642</v>
       </c>
       <c r="D37">
-        <v>126.7327601231219</v>
+        <v>125.4086637963164</v>
       </c>
       <c r="E37">
-        <v>61.27300000000001</v>
+        <v>63.06880000000001</v>
       </c>
       <c r="F37">
-        <v>62.85300000000001</v>
+        <v>64.64880000000001</v>
       </c>
       <c r="G37">
         <v>6.66</v>
@@ -4568,37 +4568,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M37">
-        <v>12.6208824</v>
+        <v>12.98147904</v>
       </c>
       <c r="N37">
-        <v>-5.603382400000004</v>
+        <v>-5.963979040000003</v>
       </c>
       <c r="O37">
-        <v>-1.400845600000001</v>
+        <v>-1.490994760000001</v>
       </c>
       <c r="P37">
-        <v>-4.202536800000003</v>
+        <v>-4.472984280000002</v>
       </c>
       <c r="Q37">
-        <v>-2.682536800000002</v>
+        <v>-2.952984280000002</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2032214166150128</v>
+        <v>0.2056811262496223</v>
       </c>
       <c r="T37">
-        <v>1.522385413084513</v>
+        <v>1.546172685163959</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.1390057322774832</v>
+        <v>0.135144461936442</v>
       </c>
       <c r="W37">
-        <v>0.1728876489586814</v>
+        <v>0.1736629920431624</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5560229291099328</v>
+        <v>0.540577847745768</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4614,22 +4614,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1941545979352968</v>
+        <v>0.1957045979352968</v>
       </c>
       <c r="C38">
-        <v>67.41986379631636</v>
+        <v>64.32734954230671</v>
       </c>
       <c r="D38">
-        <v>125.4086637963164</v>
+        <v>124.1119495423067</v>
       </c>
       <c r="E38">
-        <v>63.06880000000001</v>
+        <v>64.86460000000001</v>
       </c>
       <c r="F38">
-        <v>64.64880000000001</v>
+        <v>66.44460000000001</v>
       </c>
       <c r="G38">
         <v>6.66</v>
@@ -4650,37 +4650,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M38">
-        <v>12.98147904</v>
+        <v>13.34207568</v>
       </c>
       <c r="N38">
-        <v>-5.963979040000003</v>
+        <v>-6.324575680000003</v>
       </c>
       <c r="O38">
-        <v>-1.490994760000001</v>
+        <v>-1.581143920000001</v>
       </c>
       <c r="P38">
-        <v>-4.472984280000002</v>
+        <v>-4.743431760000003</v>
       </c>
       <c r="Q38">
-        <v>-2.952984280000002</v>
+        <v>-3.223431760000002</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2056811262496223</v>
+        <v>0.2082189219043782</v>
       </c>
       <c r="T38">
-        <v>1.546172685163958</v>
+        <v>1.57071510873799</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.135144461936442</v>
+        <v>0.1314919089111327</v>
       </c>
       <c r="W38">
-        <v>0.1736629920431624</v>
+        <v>0.1743964246906446</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.540577847745768</v>
+        <v>0.525967635644531</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4696,22 +4696,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1957045979352968</v>
+        <v>0.1972545979352968</v>
       </c>
       <c r="C39">
-        <v>64.32734954230671</v>
+        <v>61.26137666929323</v>
       </c>
       <c r="D39">
-        <v>124.1119495423067</v>
+        <v>122.8417766692932</v>
       </c>
       <c r="E39">
-        <v>64.86460000000001</v>
+        <v>66.66040000000001</v>
       </c>
       <c r="F39">
-        <v>66.44460000000001</v>
+        <v>68.24040000000001</v>
       </c>
       <c r="G39">
         <v>6.66</v>
@@ -4732,37 +4732,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M39">
-        <v>13.34207568</v>
+        <v>13.70267232</v>
       </c>
       <c r="N39">
-        <v>-6.324575680000003</v>
+        <v>-6.685172320000002</v>
       </c>
       <c r="O39">
-        <v>-1.581143920000001</v>
+        <v>-1.671293080000001</v>
       </c>
       <c r="P39">
-        <v>-4.743431760000003</v>
+        <v>-5.013879240000001</v>
       </c>
       <c r="Q39">
-        <v>-3.223431760000002</v>
+        <v>-3.493879240000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2082189219043782</v>
+        <v>0.210838581935094</v>
       </c>
       <c r="T39">
-        <v>1.57071510873799</v>
+        <v>1.596049223395054</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1314919089111327</v>
+        <v>0.1280315955187345</v>
       </c>
       <c r="W39">
-        <v>0.1743964246906446</v>
+        <v>0.1750912556198381</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.525967635644531</v>
+        <v>0.5121263820749381</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4778,22 +4778,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1972545979352968</v>
+        <v>0.213231314852065</v>
       </c>
       <c r="C40">
-        <v>61.26137666929323</v>
+        <v>47.74370556571718</v>
       </c>
       <c r="D40">
-        <v>122.8417766692932</v>
+        <v>111.1199055657172</v>
       </c>
       <c r="E40">
-        <v>66.66040000000001</v>
+        <v>68.45620000000001</v>
       </c>
       <c r="F40">
-        <v>68.24040000000001</v>
+        <v>70.03620000000001</v>
       </c>
       <c r="G40">
         <v>6.66</v>
@@ -4814,45 +4814,45 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M40">
-        <v>13.70267232</v>
+        <v>16.51453596</v>
       </c>
       <c r="N40">
-        <v>-6.685172320000002</v>
+        <v>-9.497035960000005</v>
       </c>
       <c r="O40">
-        <v>-1.671293080000001</v>
+        <v>-2.374258990000001</v>
       </c>
       <c r="P40">
-        <v>-5.013879240000001</v>
+        <v>-7.122776970000004</v>
       </c>
       <c r="Q40">
-        <v>-3.493879240000001</v>
+        <v>-5.602776970000003</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.210838581935094</v>
+        <v>0.2148174388795517</v>
       </c>
       <c r="T40">
-        <v>1.596049223395054</v>
+        <v>1.634527811018275</v>
       </c>
       <c r="U40">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.1280315955187345</v>
+        <v>0.1062321705102273</v>
       </c>
       <c r="W40">
-        <v>0.1750912556198381</v>
+        <v>0.2107504541936884</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y40">
-        <v>0.5121263820749381</v>
+        <v>0.4249286820409089</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4860,22 +4860,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.213231314852065</v>
+        <v>0.215131314852065</v>
       </c>
       <c r="C41">
-        <v>47.74370556571718</v>
+        <v>44.70107286522516</v>
       </c>
       <c r="D41">
-        <v>111.1199055657172</v>
+        <v>109.8730728652252</v>
       </c>
       <c r="E41">
-        <v>68.45620000000001</v>
+        <v>70.25200000000001</v>
       </c>
       <c r="F41">
-        <v>70.03620000000001</v>
+        <v>71.83200000000001</v>
       </c>
       <c r="G41">
         <v>6.66</v>
@@ -4896,37 +4896,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M41">
-        <v>16.51453596</v>
+        <v>16.9379856</v>
       </c>
       <c r="N41">
-        <v>-9.497035960000005</v>
+        <v>-9.920485600000003</v>
       </c>
       <c r="O41">
-        <v>-2.374258990000001</v>
+        <v>-2.480121400000001</v>
       </c>
       <c r="P41">
-        <v>-7.122776970000004</v>
+        <v>-7.440364200000002</v>
       </c>
       <c r="Q41">
-        <v>-5.602776970000003</v>
+        <v>-5.920364200000002</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2148174388795517</v>
+        <v>0.2176343961942108</v>
       </c>
       <c r="T41">
-        <v>1.634527811018275</v>
+        <v>1.661769941201913</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.1062321705102273</v>
+        <v>0.1035763662474716</v>
       </c>
       <c r="W41">
-        <v>0.2107504541936884</v>
+        <v>0.2113766928388462</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4249286820409089</v>
+        <v>0.4143054649898863</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4942,22 +4942,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.215131314852065</v>
+        <v>0.217031314852065</v>
       </c>
       <c r="C42">
-        <v>44.70107286522516</v>
+        <v>41.68611012840755</v>
       </c>
       <c r="D42">
-        <v>109.8730728652252</v>
+        <v>108.6539101284076</v>
       </c>
       <c r="E42">
-        <v>70.25200000000001</v>
+        <v>72.04780000000001</v>
       </c>
       <c r="F42">
-        <v>71.83200000000001</v>
+        <v>73.62780000000001</v>
       </c>
       <c r="G42">
         <v>6.66</v>
@@ -4978,37 +4978,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M42">
-        <v>16.9379856</v>
+        <v>17.36143524</v>
       </c>
       <c r="N42">
-        <v>-9.920485600000003</v>
+        <v>-10.34393524</v>
       </c>
       <c r="O42">
-        <v>-2.480121400000001</v>
+        <v>-2.585983810000001</v>
       </c>
       <c r="P42">
-        <v>-7.440364200000002</v>
+        <v>-7.757951430000003</v>
       </c>
       <c r="Q42">
-        <v>-5.920364200000002</v>
+        <v>-6.237951430000003</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2176343961942108</v>
+        <v>0.2205468435873331</v>
       </c>
       <c r="T42">
-        <v>1.661769941201913</v>
+        <v>1.689935533425674</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.1035763662474716</v>
+        <v>0.1010501134121674</v>
       </c>
       <c r="W42">
-        <v>0.2113766928388462</v>
+        <v>0.2119723832574109</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4143054649898863</v>
+        <v>0.4042004536486695</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5024,22 +5024,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.217031314852065</v>
+        <v>0.218931314852065</v>
       </c>
       <c r="C43">
-        <v>41.68611012840755</v>
+        <v>38.69790637741438</v>
       </c>
       <c r="D43">
-        <v>108.6539101284076</v>
+        <v>107.4615063774144</v>
       </c>
       <c r="E43">
-        <v>72.04780000000001</v>
+        <v>73.84360000000001</v>
       </c>
       <c r="F43">
-        <v>73.62780000000001</v>
+        <v>75.42360000000001</v>
       </c>
       <c r="G43">
         <v>6.66</v>
@@ -5060,37 +5060,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M43">
-        <v>17.36143524</v>
+        <v>17.78488488</v>
       </c>
       <c r="N43">
-        <v>-10.34393524</v>
+        <v>-10.76738488000001</v>
       </c>
       <c r="O43">
-        <v>-2.585983810000001</v>
+        <v>-2.691846220000001</v>
       </c>
       <c r="P43">
-        <v>-7.757951430000003</v>
+        <v>-8.075538660000003</v>
       </c>
       <c r="Q43">
-        <v>-6.237951430000003</v>
+        <v>-6.555538660000003</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2205468435873331</v>
+        <v>0.2235597202009078</v>
       </c>
       <c r="T43">
-        <v>1.689935533425674</v>
+        <v>1.719072352967496</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.1010501134121674</v>
+        <v>0.0986441583309253</v>
       </c>
       <c r="W43">
-        <v>0.2119723832574109</v>
+        <v>0.2125397074655678</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4042004536486695</v>
+        <v>0.3945766333237012</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5106,22 +5106,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.218931314852065</v>
+        <v>0.220831314852065</v>
       </c>
       <c r="C44">
-        <v>38.69790637741438</v>
+        <v>35.73559018978447</v>
       </c>
       <c r="D44">
-        <v>107.4615063774144</v>
+        <v>106.2949901897845</v>
       </c>
       <c r="E44">
-        <v>73.84360000000001</v>
+        <v>75.63940000000001</v>
       </c>
       <c r="F44">
-        <v>75.42360000000001</v>
+        <v>77.21940000000001</v>
       </c>
       <c r="G44">
         <v>6.66</v>
@@ -5142,37 +5142,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M44">
-        <v>17.78488488</v>
+        <v>18.20833452</v>
       </c>
       <c r="N44">
-        <v>-10.76738488000001</v>
+        <v>-11.19083452</v>
       </c>
       <c r="O44">
-        <v>-2.691846220000001</v>
+        <v>-2.797708630000001</v>
       </c>
       <c r="P44">
-        <v>-8.075538660000003</v>
+        <v>-8.393125890000002</v>
       </c>
       <c r="Q44">
-        <v>-6.555538660000003</v>
+        <v>-6.873125890000002</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2235597202009078</v>
+        <v>0.2266783117833799</v>
       </c>
       <c r="T44">
-        <v>1.719072352967496</v>
+        <v>1.749231517054645</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.0986441583309253</v>
+        <v>0.09635010813718287</v>
       </c>
       <c r="W44">
-        <v>0.2125397074655678</v>
+        <v>0.2130806445012523</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3945766333237012</v>
+        <v>0.3854004325487315</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5188,22 +5188,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.220831314852065</v>
+        <v>0.222731314852065</v>
       </c>
       <c r="C45">
-        <v>35.73559018978447</v>
+        <v>32.79832757459134</v>
       </c>
       <c r="D45">
-        <v>106.2949901897845</v>
+        <v>105.1535275745914</v>
       </c>
       <c r="E45">
-        <v>75.63940000000001</v>
+        <v>77.43520000000001</v>
       </c>
       <c r="F45">
-        <v>77.21940000000001</v>
+        <v>79.01520000000001</v>
       </c>
       <c r="G45">
         <v>6.66</v>
@@ -5224,37 +5224,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M45">
-        <v>18.20833452</v>
+        <v>18.63178416</v>
       </c>
       <c r="N45">
-        <v>-11.19083452</v>
+        <v>-11.61428416</v>
       </c>
       <c r="O45">
-        <v>-2.797708630000001</v>
+        <v>-2.903571040000001</v>
       </c>
       <c r="P45">
-        <v>-8.393125890000002</v>
+        <v>-8.710713120000003</v>
       </c>
       <c r="Q45">
-        <v>-6.873125890000002</v>
+        <v>-7.190713120000003</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2266783117833799</v>
+        <v>0.2299082816366545</v>
       </c>
       <c r="T45">
-        <v>1.749231517054645</v>
+        <v>1.780467794144907</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.09635010813718287</v>
+        <v>0.09416033295224689</v>
       </c>
       <c r="W45">
-        <v>0.2130806445012523</v>
+        <v>0.2135969934898602</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3854004325487315</v>
+        <v>0.3766413318089875</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5270,22 +5270,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.222731314852065</v>
+        <v>0.224631314852065</v>
       </c>
       <c r="C46">
-        <v>32.79832757459134</v>
+        <v>29.88531998398007</v>
       </c>
       <c r="D46">
-        <v>105.1535275745914</v>
+        <v>104.0363199839801</v>
       </c>
       <c r="E46">
-        <v>77.43520000000001</v>
+        <v>79.23100000000001</v>
       </c>
       <c r="F46">
-        <v>79.01520000000001</v>
+        <v>80.81100000000001</v>
       </c>
       <c r="G46">
         <v>6.66</v>
@@ -5306,37 +5306,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M46">
-        <v>18.63178416</v>
+        <v>19.0552338</v>
       </c>
       <c r="N46">
-        <v>-11.61428416</v>
+        <v>-12.03773380000001</v>
       </c>
       <c r="O46">
-        <v>-2.903571040000001</v>
+        <v>-3.009433450000001</v>
       </c>
       <c r="P46">
-        <v>-8.710713120000003</v>
+        <v>-9.028300350000004</v>
       </c>
       <c r="Q46">
-        <v>-7.190713120000003</v>
+        <v>-7.508300350000003</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2299082816366545</v>
+        <v>0.2332557049391391</v>
       </c>
       <c r="T46">
-        <v>1.780467794144907</v>
+        <v>1.812839935856632</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.09416033295224689</v>
+        <v>0.09206788110886362</v>
       </c>
       <c r="W46">
-        <v>0.2135969934898602</v>
+        <v>0.2140903936345299</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3766413318089875</v>
+        <v>0.3682715244354544</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5352,22 +5352,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.224631314852065</v>
+        <v>0.226531314852065</v>
       </c>
       <c r="C47">
-        <v>29.88531998398007</v>
+        <v>26.99580245012953</v>
       </c>
       <c r="D47">
-        <v>104.0363199839801</v>
+        <v>102.9426024501295</v>
       </c>
       <c r="E47">
-        <v>79.23100000000001</v>
+        <v>81.02680000000001</v>
       </c>
       <c r="F47">
-        <v>80.81100000000001</v>
+        <v>82.60680000000001</v>
       </c>
       <c r="G47">
         <v>6.66</v>
@@ -5388,37 +5388,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M47">
-        <v>19.0552338</v>
+        <v>19.47868344</v>
       </c>
       <c r="N47">
-        <v>-12.03773380000001</v>
+        <v>-12.46118344</v>
       </c>
       <c r="O47">
-        <v>-3.009433450000001</v>
+        <v>-3.115295860000001</v>
       </c>
       <c r="P47">
-        <v>-9.028300350000004</v>
+        <v>-9.345887580000003</v>
       </c>
       <c r="Q47">
-        <v>-7.508300350000003</v>
+        <v>-7.825887580000003</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2332557049391391</v>
+        <v>0.2367271068824565</v>
       </c>
       <c r="T47">
-        <v>1.812839935856632</v>
+        <v>1.846411045779903</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.09206788110886362</v>
+        <v>0.09006640543258398</v>
       </c>
       <c r="W47">
-        <v>0.2140903936345299</v>
+        <v>0.2145623415989967</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3682715244354544</v>
+        <v>0.3602656217303359</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5434,22 +5434,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.226531314852065</v>
+        <v>0.228431314852065</v>
       </c>
       <c r="C48">
-        <v>26.99580245012953</v>
+        <v>24.12904183850783</v>
       </c>
       <c r="D48">
-        <v>102.9426024501295</v>
+        <v>101.8716418385078</v>
       </c>
       <c r="E48">
-        <v>81.02680000000001</v>
+        <v>82.82260000000001</v>
       </c>
       <c r="F48">
-        <v>82.60680000000001</v>
+        <v>84.40260000000001</v>
       </c>
       <c r="G48">
         <v>6.66</v>
@@ -5470,37 +5470,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M48">
-        <v>19.47868344</v>
+        <v>19.90213308</v>
       </c>
       <c r="N48">
-        <v>-12.46118344</v>
+        <v>-12.88463308</v>
       </c>
       <c r="O48">
-        <v>-3.115295860000001</v>
+        <v>-3.221158270000001</v>
       </c>
       <c r="P48">
-        <v>-9.345887580000003</v>
+        <v>-9.663474810000004</v>
       </c>
       <c r="Q48">
-        <v>-7.825887580000003</v>
+        <v>-8.143474810000004</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2367271068824565</v>
+        <v>0.2403295051255217</v>
       </c>
       <c r="T48">
-        <v>1.846411045779903</v>
+        <v>1.881248990039901</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.09006640543258398</v>
+        <v>0.08815009893401836</v>
       </c>
       <c r="W48">
-        <v>0.2145623415989967</v>
+        <v>0.2150142066713585</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3602656217303359</v>
+        <v>0.3526003957360734</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5516,22 +5516,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.228431314852065</v>
+        <v>0.230331314852065</v>
       </c>
       <c r="C49">
-        <v>24.12904183850783</v>
+        <v>21.28433520903772</v>
       </c>
       <c r="D49">
-        <v>101.8716418385078</v>
+        <v>100.8227352090377</v>
       </c>
       <c r="E49">
-        <v>82.82260000000001</v>
+        <v>84.61840000000001</v>
       </c>
       <c r="F49">
-        <v>84.40260000000001</v>
+        <v>86.19840000000001</v>
       </c>
       <c r="G49">
         <v>6.66</v>
@@ -5552,37 +5552,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M49">
-        <v>19.90213308</v>
+        <v>20.32558272</v>
       </c>
       <c r="N49">
-        <v>-12.88463308</v>
+        <v>-13.30808272000001</v>
       </c>
       <c r="O49">
-        <v>-3.221158270000001</v>
+        <v>-3.327020680000001</v>
       </c>
       <c r="P49">
-        <v>-9.663474810000004</v>
+        <v>-9.981062040000005</v>
       </c>
       <c r="Q49">
-        <v>-8.143474810000004</v>
+        <v>-8.461062040000005</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2403295051255217</v>
+        <v>0.2440704571471664</v>
       </c>
       <c r="T49">
-        <v>1.881248990039901</v>
+        <v>1.917426855232977</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.08815009893401836</v>
+        <v>0.08631363853955965</v>
       </c>
       <c r="W49">
-        <v>0.2150142066713585</v>
+        <v>0.2154472440323718</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3526003957360734</v>
+        <v>0.3452545541582386</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5598,22 +5598,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.230331314852065</v>
+        <v>0.232231314852065</v>
       </c>
       <c r="C50">
-        <v>21.28433520903774</v>
+        <v>18.46100827747489</v>
       </c>
       <c r="D50">
-        <v>100.8227352090377</v>
+        <v>99.7952082774749</v>
       </c>
       <c r="E50">
-        <v>84.61840000000001</v>
+        <v>86.41420000000001</v>
       </c>
       <c r="F50">
-        <v>86.19840000000001</v>
+        <v>87.99420000000001</v>
       </c>
       <c r="G50">
         <v>6.66</v>
@@ -5634,37 +5634,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M50">
-        <v>20.32558272</v>
+        <v>20.74903236</v>
       </c>
       <c r="N50">
-        <v>-13.30808272000001</v>
+        <v>-13.73153236</v>
       </c>
       <c r="O50">
-        <v>-3.327020680000001</v>
+        <v>-3.432883090000001</v>
       </c>
       <c r="P50">
-        <v>-9.981062040000005</v>
+        <v>-10.29864927</v>
       </c>
       <c r="Q50">
-        <v>-8.461062040000005</v>
+        <v>-8.778649270000003</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2440704571471664</v>
+        <v>0.2479581131696598</v>
       </c>
       <c r="T50">
-        <v>1.917426855232976</v>
+        <v>1.955023460237545</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.08631363853955965</v>
+        <v>0.0845521357122217</v>
       </c>
       <c r="W50">
-        <v>0.2154472440323718</v>
+        <v>0.2158626063990581</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3452545541582386</v>
+        <v>0.3382085428488868</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5680,22 +5680,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.232231314852065</v>
+        <v>0.234131314852065</v>
       </c>
       <c r="C51">
-        <v>18.46100827747489</v>
+        <v>15.65841396992097</v>
       </c>
       <c r="D51">
-        <v>99.7952082774749</v>
+        <v>98.78841396992098</v>
       </c>
       <c r="E51">
-        <v>86.41420000000001</v>
+        <v>88.21000000000001</v>
       </c>
       <c r="F51">
-        <v>87.99420000000001</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="G51">
         <v>6.66</v>
@@ -5716,37 +5716,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M51">
-        <v>20.74903236</v>
+        <v>21.172482</v>
       </c>
       <c r="N51">
-        <v>-13.73153236</v>
+        <v>-14.154982</v>
       </c>
       <c r="O51">
-        <v>-3.432883090000001</v>
+        <v>-3.538745500000001</v>
       </c>
       <c r="P51">
-        <v>-10.29864927</v>
+        <v>-10.6162365</v>
       </c>
       <c r="Q51">
-        <v>-8.778649270000003</v>
+        <v>-9.096236500000003</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2479581131696598</v>
+        <v>0.252001275433053</v>
       </c>
       <c r="T51">
-        <v>1.955023460237545</v>
+        <v>1.994123929442296</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.0845521357122217</v>
+        <v>0.08286109299797727</v>
       </c>
       <c r="W51">
-        <v>0.2158626063990581</v>
+        <v>0.216261354271077</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3382085428488868</v>
+        <v>0.331444371991909</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5762,22 +5762,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.234131314852065</v>
+        <v>0.236031314852065</v>
       </c>
       <c r="C52">
-        <v>15.65841396992097</v>
+        <v>12.87593106396086</v>
       </c>
       <c r="D52">
-        <v>98.78841396992098</v>
+        <v>97.80173106396087</v>
       </c>
       <c r="E52">
-        <v>88.21000000000001</v>
+        <v>90.00580000000001</v>
       </c>
       <c r="F52">
-        <v>89.79000000000001</v>
+        <v>91.58580000000001</v>
       </c>
       <c r="G52">
         <v>6.66</v>
@@ -5798,37 +5798,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M52">
-        <v>21.172482</v>
+        <v>21.59593164</v>
       </c>
       <c r="N52">
-        <v>-14.154982</v>
+        <v>-14.57843164000001</v>
       </c>
       <c r="O52">
-        <v>-3.538745500000001</v>
+        <v>-3.644607910000001</v>
       </c>
       <c r="P52">
-        <v>-10.6162365</v>
+        <v>-10.93382373</v>
       </c>
       <c r="Q52">
-        <v>-9.096236500000003</v>
+        <v>-9.413823730000004</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.252001275433053</v>
+        <v>0.2562094647276051</v>
       </c>
       <c r="T52">
-        <v>1.994123929442296</v>
+        <v>2.034820336165608</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.08286109299797727</v>
+        <v>0.08123636568429143</v>
       </c>
       <c r="W52">
-        <v>0.216261354271077</v>
+        <v>0.2166444649716441</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.331444371991909</v>
+        <v>0.3249454627371656</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5844,22 +5844,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.236031314852065</v>
+        <v>0.237931314852065</v>
       </c>
       <c r="C53">
-        <v>12.87593106396086</v>
+        <v>10.11296291042687</v>
       </c>
       <c r="D53">
-        <v>97.80173106396087</v>
+        <v>96.83456291042688</v>
       </c>
       <c r="E53">
-        <v>90.00580000000001</v>
+        <v>91.80160000000001</v>
       </c>
       <c r="F53">
-        <v>91.58580000000001</v>
+        <v>93.38160000000001</v>
       </c>
       <c r="G53">
         <v>6.66</v>
@@ -5880,37 +5880,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M53">
-        <v>21.59593164</v>
+        <v>22.01938128</v>
       </c>
       <c r="N53">
-        <v>-14.57843164000001</v>
+        <v>-15.00188128</v>
       </c>
       <c r="O53">
-        <v>-3.644607910000001</v>
+        <v>-3.750470320000001</v>
       </c>
       <c r="P53">
-        <v>-10.93382373</v>
+        <v>-11.25141096</v>
       </c>
       <c r="Q53">
-        <v>-9.413823730000004</v>
+        <v>-9.731410960000002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2562094647276051</v>
+        <v>0.2605929952427636</v>
       </c>
       <c r="T53">
-        <v>2.034820336165608</v>
+        <v>2.077212426502391</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.08123636568429143</v>
+        <v>0.07967412788267045</v>
       </c>
       <c r="W53">
-        <v>0.2166444649716441</v>
+        <v>0.2170128406452663</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3249454627371656</v>
+        <v>0.3186965115306818</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5926,22 +5926,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.237931314852065</v>
+        <v>0.239831314852065</v>
       </c>
       <c r="C54">
-        <v>10.11296291042687</v>
+        <v>7.368936230264026</v>
       </c>
       <c r="D54">
-        <v>96.83456291042688</v>
+        <v>95.88633623026404</v>
       </c>
       <c r="E54">
-        <v>91.80160000000001</v>
+        <v>93.59740000000001</v>
       </c>
       <c r="F54">
-        <v>93.38160000000001</v>
+        <v>95.17740000000001</v>
       </c>
       <c r="G54">
         <v>6.66</v>
@@ -5962,37 +5962,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M54">
-        <v>22.01938128</v>
+        <v>22.44283092</v>
       </c>
       <c r="N54">
-        <v>-15.00188128</v>
+        <v>-15.42533092</v>
       </c>
       <c r="O54">
-        <v>-3.750470320000001</v>
+        <v>-3.856332730000001</v>
       </c>
       <c r="P54">
-        <v>-11.25141096</v>
+        <v>-11.56899819</v>
       </c>
       <c r="Q54">
-        <v>-9.731410960000002</v>
+        <v>-10.04899819</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2605929952427636</v>
+        <v>0.265163058971333</v>
       </c>
       <c r="T54">
-        <v>2.077212426502391</v>
+        <v>2.12140843557691</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.07967412788267045</v>
+        <v>0.07817084245092194</v>
       </c>
       <c r="W54">
-        <v>0.2170128406452663</v>
+        <v>0.2173673153500726</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3186965115306818</v>
+        <v>0.3126833698036877</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6008,22 +6008,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.239831314852065</v>
+        <v>0.241731314852065</v>
       </c>
       <c r="C55">
-        <v>7.368936230264026</v>
+        <v>4.643299981397604</v>
       </c>
       <c r="D55">
-        <v>95.88633623026404</v>
+        <v>94.95649998139763</v>
       </c>
       <c r="E55">
-        <v>93.59740000000001</v>
+        <v>95.39320000000002</v>
       </c>
       <c r="F55">
-        <v>95.17740000000001</v>
+        <v>96.97320000000002</v>
       </c>
       <c r="G55">
         <v>6.66</v>
@@ -6044,37 +6044,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M55">
-        <v>22.44283092</v>
+        <v>22.86628056000001</v>
       </c>
       <c r="N55">
-        <v>-15.42533092</v>
+        <v>-15.84878056000001</v>
       </c>
       <c r="O55">
-        <v>-3.856332730000001</v>
+        <v>-3.962195140000002</v>
       </c>
       <c r="P55">
-        <v>-11.56899819</v>
+        <v>-11.88658542000001</v>
       </c>
       <c r="Q55">
-        <v>-10.04899819</v>
+        <v>-10.36658542000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.265163058971333</v>
+        <v>0.2699318211228837</v>
       </c>
       <c r="T55">
-        <v>2.12140843557691</v>
+        <v>2.167526010263365</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.07817084245092194</v>
+        <v>0.07672323425738634</v>
       </c>
       <c r="W55">
-        <v>0.2173673153500726</v>
+        <v>0.2177086613621083</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3126833698036877</v>
+        <v>0.3068929370295453</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6090,22 +6090,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.241731314852065</v>
+        <v>0.243631314852065</v>
       </c>
       <c r="C56">
-        <v>4.643299981397604</v>
+        <v>1.935524290897987</v>
       </c>
       <c r="D56">
-        <v>94.95649998139763</v>
+        <v>94.04452429089801</v>
       </c>
       <c r="E56">
-        <v>95.39320000000002</v>
+        <v>97.18900000000002</v>
       </c>
       <c r="F56">
-        <v>96.97320000000002</v>
+        <v>98.76900000000002</v>
       </c>
       <c r="G56">
         <v>6.66</v>
@@ -6126,37 +6126,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M56">
-        <v>22.86628056000001</v>
+        <v>23.2897302</v>
       </c>
       <c r="N56">
-        <v>-15.84878056000001</v>
+        <v>-16.27223020000001</v>
       </c>
       <c r="O56">
-        <v>-3.962195140000002</v>
+        <v>-4.068057550000002</v>
       </c>
       <c r="P56">
-        <v>-11.88658542000001</v>
+        <v>-12.20417265</v>
       </c>
       <c r="Q56">
-        <v>-10.36658542000001</v>
+        <v>-10.68417265</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2699318211228837</v>
+        <v>0.2749125282589479</v>
       </c>
       <c r="T56">
-        <v>2.167526010263365</v>
+        <v>2.215693254935884</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.07672323425738634</v>
+        <v>0.0753282663617975</v>
       </c>
       <c r="W56">
-        <v>0.2177086613621083</v>
+        <v>0.2180375947918882</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3068929370295453</v>
+        <v>0.3013130654471899</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6172,22 +6172,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.243631314852065</v>
+        <v>0.245531314852065</v>
       </c>
       <c r="C57">
-        <v>1.935524290897987</v>
+        <v>-0.7549005519066725</v>
       </c>
       <c r="D57">
-        <v>94.04452429089801</v>
+        <v>93.14989944809335</v>
       </c>
       <c r="E57">
-        <v>97.18900000000002</v>
+        <v>98.98480000000002</v>
       </c>
       <c r="F57">
-        <v>98.76900000000002</v>
+        <v>100.5648</v>
       </c>
       <c r="G57">
         <v>6.66</v>
@@ -6208,37 +6208,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M57">
-        <v>23.2897302</v>
+        <v>23.71317984000001</v>
       </c>
       <c r="N57">
-        <v>-16.27223020000001</v>
+        <v>-16.69567984000001</v>
       </c>
       <c r="O57">
-        <v>-4.068057550000002</v>
+        <v>-4.173919960000002</v>
       </c>
       <c r="P57">
-        <v>-12.20417265</v>
+        <v>-12.52175988</v>
       </c>
       <c r="Q57">
-        <v>-10.68417265</v>
+        <v>-11.00175988000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2749125282589479</v>
+        <v>0.2801196311739239</v>
       </c>
       <c r="T57">
-        <v>2.215693254935884</v>
+        <v>2.26604991982079</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.0753282663617975</v>
+        <v>0.07398311874819398</v>
       </c>
       <c r="W57">
-        <v>0.2180375947918882</v>
+        <v>0.2183547805991759</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3013130654471899</v>
+        <v>0.2959324749927759</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6254,22 +6254,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.245531314852065</v>
+        <v>0.247431314852065</v>
       </c>
       <c r="C58">
-        <v>-0.7549005519066725</v>
+        <v>-3.428465045389416</v>
       </c>
       <c r="D58">
-        <v>93.14989944809335</v>
+        <v>92.27213495461061</v>
       </c>
       <c r="E58">
-        <v>98.98480000000002</v>
+        <v>100.7806</v>
       </c>
       <c r="F58">
-        <v>100.5648</v>
+        <v>102.3606</v>
       </c>
       <c r="G58">
         <v>6.66</v>
@@ -6290,37 +6290,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M58">
-        <v>23.71317984000001</v>
+        <v>24.13662948000001</v>
       </c>
       <c r="N58">
-        <v>-16.69567984000001</v>
+        <v>-17.11912948000001</v>
       </c>
       <c r="O58">
-        <v>-4.173919960000002</v>
+        <v>-4.279782370000002</v>
       </c>
       <c r="P58">
-        <v>-12.52175988</v>
+        <v>-12.83934711000001</v>
       </c>
       <c r="Q58">
-        <v>-11.00175988000001</v>
+        <v>-11.31934711000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2801196311739239</v>
+        <v>0.2855689249221547</v>
       </c>
       <c r="T58">
-        <v>2.26604991982079</v>
+        <v>2.318748755165461</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.07398311874819398</v>
+        <v>0.07268516929647127</v>
       </c>
       <c r="W58">
-        <v>0.2183547805991759</v>
+        <v>0.2186608370798921</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2959324749927759</v>
+        <v>0.290740677185885</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6336,22 +6336,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.247431314852065</v>
+        <v>0.249331314852065</v>
       </c>
       <c r="C59">
-        <v>-3.428465045389416</v>
+        <v>-6.085641372374724</v>
       </c>
       <c r="D59">
-        <v>92.27213495461061</v>
+        <v>91.4107586276253</v>
       </c>
       <c r="E59">
-        <v>100.7806</v>
+        <v>102.5764</v>
       </c>
       <c r="F59">
-        <v>102.3606</v>
+        <v>104.1564</v>
       </c>
       <c r="G59">
         <v>6.66</v>
@@ -6372,37 +6372,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M59">
-        <v>24.13662948000001</v>
+        <v>24.56007912</v>
       </c>
       <c r="N59">
-        <v>-17.11912948000001</v>
+        <v>-17.54257912000001</v>
       </c>
       <c r="O59">
-        <v>-4.279782370000002</v>
+        <v>-4.385644780000002</v>
       </c>
       <c r="P59">
-        <v>-12.83934711000001</v>
+        <v>-13.15693434</v>
       </c>
       <c r="Q59">
-        <v>-11.31934711000001</v>
+        <v>-11.63693434</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2855689249221547</v>
+        <v>0.2912777088488727</v>
       </c>
       <c r="T59">
-        <v>2.318748755165461</v>
+        <v>2.373957058859876</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.07268516929647127</v>
+        <v>0.07143197672239418</v>
       </c>
       <c r="W59">
-        <v>0.2186608370798921</v>
+        <v>0.2189563398888595</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.290740677185885</v>
+        <v>0.2857279068895767</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6418,22 +6418,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.249331314852065</v>
+        <v>0.251231314852065</v>
       </c>
       <c r="C60">
-        <v>-6.085641372374681</v>
+        <v>-8.726884247126065</v>
       </c>
       <c r="D60">
-        <v>91.41075862762533</v>
+        <v>90.56531575287394</v>
       </c>
       <c r="E60">
-        <v>102.5764</v>
+        <v>104.3722</v>
       </c>
       <c r="F60">
-        <v>104.1564</v>
+        <v>105.9522</v>
       </c>
       <c r="G60">
         <v>6.66</v>
@@ -6454,37 +6454,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M60">
-        <v>24.56007912</v>
+        <v>24.98352876</v>
       </c>
       <c r="N60">
-        <v>-17.54257912</v>
+        <v>-17.96602876</v>
       </c>
       <c r="O60">
-        <v>-4.385644780000001</v>
+        <v>-4.491507190000001</v>
       </c>
       <c r="P60">
-        <v>-13.15693434</v>
+        <v>-13.47452157</v>
       </c>
       <c r="Q60">
-        <v>-11.63693434</v>
+        <v>-11.95452157</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2912777088488726</v>
+        <v>0.2972649700403085</v>
       </c>
       <c r="T60">
-        <v>2.373957058859876</v>
+        <v>2.431858450539384</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.07143197672239419</v>
+        <v>0.0702212652525231</v>
       </c>
       <c r="W60">
-        <v>0.2189563398888595</v>
+        <v>0.219241825653455</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2857279068895767</v>
+        <v>0.2808850610100924</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6500,22 +6500,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.251231314852065</v>
+        <v>0.253131314852065</v>
       </c>
       <c r="C61">
-        <v>-8.726884247126065</v>
+        <v>-11.35263171576214</v>
       </c>
       <c r="D61">
-        <v>90.56531575287394</v>
+        <v>89.73536828423786</v>
       </c>
       <c r="E61">
-        <v>104.3722</v>
+        <v>106.168</v>
       </c>
       <c r="F61">
-        <v>105.9522</v>
+        <v>107.748</v>
       </c>
       <c r="G61">
         <v>6.66</v>
@@ -6536,37 +6536,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M61">
-        <v>24.98352876</v>
+        <v>25.4069784</v>
       </c>
       <c r="N61">
-        <v>-17.96602876</v>
+        <v>-18.38947840000001</v>
       </c>
       <c r="O61">
-        <v>-4.491507190000001</v>
+        <v>-4.597369600000001</v>
       </c>
       <c r="P61">
-        <v>-13.47452157</v>
+        <v>-13.7921088</v>
       </c>
       <c r="Q61">
-        <v>-11.95452157</v>
+        <v>-12.27210880000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2972649700403085</v>
+        <v>0.3035515942913162</v>
       </c>
       <c r="T61">
-        <v>2.431858450539384</v>
+        <v>2.492654911802869</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.0702212652525231</v>
+        <v>0.06905091083164772</v>
       </c>
       <c r="W61">
-        <v>0.219241825653455</v>
+        <v>0.2195177952258975</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2808850610100924</v>
+        <v>0.2762036433265909</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6582,22 +6582,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.253131314852065</v>
+        <v>0.255031314852065</v>
       </c>
       <c r="C62">
-        <v>-11.35263171576214</v>
+        <v>-13.96330591306193</v>
       </c>
       <c r="D62">
-        <v>89.73536828423786</v>
+        <v>88.92049408693808</v>
       </c>
       <c r="E62">
-        <v>106.168</v>
+        <v>107.9638</v>
       </c>
       <c r="F62">
-        <v>107.748</v>
+        <v>109.5438</v>
       </c>
       <c r="G62">
         <v>6.66</v>
@@ -6618,37 +6618,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M62">
-        <v>25.4069784</v>
+        <v>25.83042804</v>
       </c>
       <c r="N62">
-        <v>-18.38947840000001</v>
+        <v>-18.81292804</v>
       </c>
       <c r="O62">
-        <v>-4.597369600000001</v>
+        <v>-4.703232010000001</v>
       </c>
       <c r="P62">
-        <v>-13.7921088</v>
+        <v>-14.10969603</v>
       </c>
       <c r="Q62">
-        <v>-12.27210880000001</v>
+        <v>-12.58969603</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3035515942913162</v>
+        <v>0.3101606095295552</v>
       </c>
       <c r="T62">
-        <v>2.492654911802869</v>
+        <v>2.556569140310635</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.06905091083164772</v>
+        <v>0.06791892868686661</v>
       </c>
       <c r="W62">
-        <v>0.2195177952258975</v>
+        <v>0.2197847166156368</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2762036433265909</v>
+        <v>0.2716757147474664</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6664,22 +6664,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.255031314852065</v>
+        <v>0.256931314852065</v>
       </c>
       <c r="C63">
-        <v>-13.96330591306193</v>
+        <v>-16.55931377840659</v>
       </c>
       <c r="D63">
-        <v>88.92049408693808</v>
+        <v>88.12028622159342</v>
       </c>
       <c r="E63">
-        <v>107.9638</v>
+        <v>109.7596</v>
       </c>
       <c r="F63">
-        <v>109.5438</v>
+        <v>111.3396</v>
       </c>
       <c r="G63">
         <v>6.66</v>
@@ -6700,37 +6700,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M63">
-        <v>25.83042804</v>
+        <v>26.25387768</v>
       </c>
       <c r="N63">
-        <v>-18.81292804</v>
+        <v>-19.23637768</v>
       </c>
       <c r="O63">
-        <v>-4.703232010000001</v>
+        <v>-4.809094420000001</v>
       </c>
       <c r="P63">
-        <v>-14.10969603</v>
+        <v>-14.42728326</v>
       </c>
       <c r="Q63">
-        <v>-12.58969603</v>
+        <v>-12.90728326</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3101606095295552</v>
+        <v>0.3171174676750698</v>
       </c>
       <c r="T63">
-        <v>2.556569140310635</v>
+        <v>2.623847275581968</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.06791892868686661</v>
+        <v>0.06682346209514295</v>
       </c>
       <c r="W63">
-        <v>0.2197847166156368</v>
+        <v>0.2200430276379653</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2716757147474664</v>
+        <v>0.2672938483805718</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6746,22 +6746,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.256931314852065</v>
+        <v>0.258831314852065</v>
       </c>
       <c r="C64">
-        <v>-16.55931377840659</v>
+        <v>-19.14104773340891</v>
       </c>
       <c r="D64">
-        <v>88.12028622159342</v>
+        <v>87.3343522665911</v>
       </c>
       <c r="E64">
-        <v>109.7596</v>
+        <v>111.5554</v>
       </c>
       <c r="F64">
-        <v>111.3396</v>
+        <v>113.1354</v>
       </c>
       <c r="G64">
         <v>6.66</v>
@@ -6782,37 +6782,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M64">
-        <v>26.25387768</v>
+        <v>26.67732732</v>
       </c>
       <c r="N64">
-        <v>-19.23637768</v>
+        <v>-19.65982732000001</v>
       </c>
       <c r="O64">
-        <v>-4.809094420000001</v>
+        <v>-4.914956830000001</v>
       </c>
       <c r="P64">
-        <v>-14.42728326</v>
+        <v>-14.74487049</v>
       </c>
       <c r="Q64">
-        <v>-12.90728326</v>
+        <v>-13.22487049</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3171174676750698</v>
+        <v>0.3244503722068284</v>
       </c>
       <c r="T64">
-        <v>2.623847275581968</v>
+        <v>2.694762066813913</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.06682346209514295</v>
+        <v>0.06576277222061687</v>
       </c>
       <c r="W64">
-        <v>0.2200430276379653</v>
+        <v>0.2202931383103786</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2672938483805718</v>
+        <v>0.2630510888824674</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6828,22 +6828,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.258831314852065</v>
+        <v>0.260731314852065</v>
       </c>
       <c r="C65">
-        <v>-19.14104773340891</v>
+        <v>-21.70888632360101</v>
       </c>
       <c r="D65">
-        <v>87.3343522665911</v>
+        <v>86.562313676399</v>
       </c>
       <c r="E65">
-        <v>111.5554</v>
+        <v>113.3512</v>
       </c>
       <c r="F65">
-        <v>113.1354</v>
+        <v>114.9312</v>
       </c>
       <c r="G65">
         <v>6.66</v>
@@ -6864,37 +6864,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M65">
-        <v>26.67732732</v>
+        <v>27.10077696</v>
       </c>
       <c r="N65">
-        <v>-19.65982732000001</v>
+        <v>-20.08327696</v>
       </c>
       <c r="O65">
-        <v>-4.914956830000001</v>
+        <v>-5.020819240000001</v>
       </c>
       <c r="P65">
-        <v>-14.74487049</v>
+        <v>-15.06245772</v>
       </c>
       <c r="Q65">
-        <v>-13.22487049</v>
+        <v>-13.54245772</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3244503722068284</v>
+        <v>0.3321906603236847</v>
       </c>
       <c r="T65">
-        <v>2.694762066813913</v>
+        <v>2.769616568669855</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06576277222061687</v>
+        <v>0.06473522890466973</v>
       </c>
       <c r="W65">
-        <v>0.2202931383103786</v>
+        <v>0.2205354330242789</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2630510888824674</v>
+        <v>0.2589409156186789</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6910,22 +6910,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.260731314852065</v>
+        <v>0.262631314852065</v>
       </c>
       <c r="C66">
-        <v>-21.70888632360101</v>
+        <v>-24.26319482638519</v>
       </c>
       <c r="D66">
-        <v>86.562313676399</v>
+        <v>85.80380517361483</v>
       </c>
       <c r="E66">
-        <v>113.3512</v>
+        <v>115.147</v>
       </c>
       <c r="F66">
-        <v>114.9312</v>
+        <v>116.727</v>
       </c>
       <c r="G66">
         <v>6.66</v>
@@ -6946,37 +6946,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M66">
-        <v>27.10077696</v>
+        <v>27.52422660000001</v>
       </c>
       <c r="N66">
-        <v>-20.08327696</v>
+        <v>-20.50672660000001</v>
       </c>
       <c r="O66">
-        <v>-5.020819240000001</v>
+        <v>-5.126681650000002</v>
       </c>
       <c r="P66">
-        <v>-15.06245772</v>
+        <v>-15.38004495000001</v>
       </c>
       <c r="Q66">
-        <v>-13.54245772</v>
+        <v>-13.86004495000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3321906603236847</v>
+        <v>0.3403732506186472</v>
       </c>
       <c r="T66">
-        <v>2.769616568669855</v>
+        <v>2.848748470631851</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.06473522890466973</v>
+        <v>0.06373930230613635</v>
       </c>
       <c r="W66">
-        <v>0.2205354330242789</v>
+        <v>0.2207702725162131</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2589409156186789</v>
+        <v>0.2549572092245453</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6992,22 +6992,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.262631314852065</v>
+        <v>0.264531314852065</v>
       </c>
       <c r="C67">
-        <v>-24.26319482638519</v>
+        <v>-26.80432582729894</v>
       </c>
       <c r="D67">
-        <v>85.80380517361483</v>
+        <v>85.05847417270108</v>
       </c>
       <c r="E67">
-        <v>115.147</v>
+        <v>116.9428</v>
       </c>
       <c r="F67">
-        <v>116.727</v>
+        <v>118.5228</v>
       </c>
       <c r="G67">
         <v>6.66</v>
@@ -7028,37 +7028,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M67">
-        <v>27.52422660000001</v>
+        <v>27.94767624000001</v>
       </c>
       <c r="N67">
-        <v>-20.50672660000001</v>
+        <v>-20.93017624000001</v>
       </c>
       <c r="O67">
-        <v>-5.126681650000002</v>
+        <v>-5.232544060000002</v>
       </c>
       <c r="P67">
-        <v>-15.38004495000001</v>
+        <v>-15.69763218000001</v>
       </c>
       <c r="Q67">
-        <v>-13.86004495000001</v>
+        <v>-14.17763218000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3403732506186472</v>
+        <v>0.3490371697544897</v>
       </c>
       <c r="T67">
-        <v>2.848748470631851</v>
+        <v>2.932535190356317</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.06373930230613635</v>
+        <v>0.06277355530149792</v>
       </c>
       <c r="W67">
-        <v>0.2207702725162131</v>
+        <v>0.2209979956599068</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2549572092245453</v>
+        <v>0.2510942212059917</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7074,22 +7074,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.264531314852065</v>
+        <v>0.2664313148520651</v>
       </c>
       <c r="C68">
-        <v>-26.80432582729894</v>
+        <v>-29.33261976650469</v>
       </c>
       <c r="D68">
-        <v>85.05847417270108</v>
+        <v>84.32598023349533</v>
       </c>
       <c r="E68">
-        <v>116.9428</v>
+        <v>118.7386</v>
       </c>
       <c r="F68">
-        <v>118.5228</v>
+        <v>120.3186</v>
       </c>
       <c r="G68">
         <v>6.66</v>
@@ -7110,37 +7110,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M68">
-        <v>27.94767624000001</v>
+        <v>28.37112588</v>
       </c>
       <c r="N68">
-        <v>-20.93017624000001</v>
+        <v>-21.35362588000001</v>
       </c>
       <c r="O68">
-        <v>-5.232544060000002</v>
+        <v>-5.338406470000002</v>
       </c>
       <c r="P68">
-        <v>-15.69763218000001</v>
+        <v>-16.01521941</v>
       </c>
       <c r="Q68">
-        <v>-14.17763218000001</v>
+        <v>-14.49521941</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3490371697544897</v>
+        <v>0.3582261748985652</v>
       </c>
       <c r="T68">
-        <v>2.932535190356317</v>
+        <v>3.021399893094388</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.06277355530149792</v>
+        <v>0.06183663656565467</v>
       </c>
       <c r="W68">
-        <v>0.2209979956599068</v>
+        <v>0.2212189210978187</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2510942212059917</v>
+        <v>0.2473465462626186</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7156,22 +7156,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2664313148520651</v>
+        <v>0.268331314852065</v>
       </c>
       <c r="C69">
-        <v>-29.33261976650469</v>
+        <v>-31.84840545728331</v>
       </c>
       <c r="D69">
-        <v>84.32598023349533</v>
+        <v>83.60599454271672</v>
       </c>
       <c r="E69">
-        <v>118.7386</v>
+        <v>120.5344</v>
       </c>
       <c r="F69">
-        <v>120.3186</v>
+        <v>122.1144</v>
       </c>
       <c r="G69">
         <v>6.66</v>
@@ -7192,37 +7192,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M69">
-        <v>28.37112588</v>
+        <v>28.79457552000001</v>
       </c>
       <c r="N69">
-        <v>-21.35362588000001</v>
+        <v>-21.77707552000001</v>
       </c>
       <c r="O69">
-        <v>-5.338406470000002</v>
+        <v>-5.444268880000002</v>
       </c>
       <c r="P69">
-        <v>-16.01521941</v>
+        <v>-16.33280664</v>
       </c>
       <c r="Q69">
-        <v>-14.49521941</v>
+        <v>-14.81280664000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3582261748985652</v>
+        <v>0.3679894928641454</v>
       </c>
       <c r="T69">
-        <v>3.021399893094388</v>
+        <v>3.115818639753587</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.06183663656565467</v>
+        <v>0.06092727426321857</v>
       </c>
       <c r="W69">
-        <v>0.2212189210978187</v>
+        <v>0.2214333487287331</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2473465462626186</v>
+        <v>0.2437090970528742</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7238,22 +7238,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.268331314852065</v>
+        <v>0.270231314852065</v>
       </c>
       <c r="C70">
-        <v>-31.84840545728331</v>
+        <v>-34.35200057819085</v>
       </c>
       <c r="D70">
-        <v>83.60599454271672</v>
+        <v>82.89819942180917</v>
       </c>
       <c r="E70">
-        <v>120.5344</v>
+        <v>122.3302</v>
       </c>
       <c r="F70">
-        <v>122.1144</v>
+        <v>123.9102</v>
       </c>
       <c r="G70">
         <v>6.66</v>
@@ -7274,37 +7274,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M70">
-        <v>28.79457552000001</v>
+        <v>29.21802516000001</v>
       </c>
       <c r="N70">
-        <v>-21.77707552000001</v>
+        <v>-22.20052516000001</v>
       </c>
       <c r="O70">
-        <v>-5.444268880000002</v>
+        <v>-5.550131290000002</v>
       </c>
       <c r="P70">
-        <v>-16.33280664</v>
+        <v>-16.65039387000001</v>
       </c>
       <c r="Q70">
-        <v>-14.81280664000001</v>
+        <v>-15.13039387000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3679894928641454</v>
+        <v>0.3783827023113759</v>
       </c>
       <c r="T70">
-        <v>3.115818639753587</v>
+        <v>3.216328918455316</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.06092727426321857</v>
+        <v>0.06004427028838931</v>
       </c>
       <c r="W70">
-        <v>0.2214333487287331</v>
+        <v>0.2216415610659978</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2437090970528742</v>
+        <v>0.2401770811535572</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7320,22 +7320,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.270231314852065</v>
+        <v>0.272131314852065</v>
       </c>
       <c r="C71">
-        <v>-34.35200057819085</v>
+        <v>-36.84371214042604</v>
       </c>
       <c r="D71">
-        <v>82.89819942180917</v>
+        <v>82.20228785957399</v>
       </c>
       <c r="E71">
-        <v>122.3302</v>
+        <v>124.126</v>
       </c>
       <c r="F71">
-        <v>123.9102</v>
+        <v>125.706</v>
       </c>
       <c r="G71">
         <v>6.66</v>
@@ -7356,37 +7356,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M71">
-        <v>29.21802516000001</v>
+        <v>29.6414748</v>
       </c>
       <c r="N71">
-        <v>-22.20052516000001</v>
+        <v>-22.62397480000001</v>
       </c>
       <c r="O71">
-        <v>-5.550131290000002</v>
+        <v>-5.655993700000002</v>
       </c>
       <c r="P71">
-        <v>-16.65039387000001</v>
+        <v>-16.9679811</v>
       </c>
       <c r="Q71">
-        <v>-15.13039387000001</v>
+        <v>-15.4479811</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3783827023113759</v>
+        <v>0.3894687923884218</v>
       </c>
       <c r="T71">
-        <v>3.216328918455316</v>
+        <v>3.323539882403827</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.06004427028838931</v>
+        <v>0.05918649499855518</v>
       </c>
       <c r="W71">
-        <v>0.2216415610659978</v>
+        <v>0.2218438244793407</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2401770811535572</v>
+        <v>0.2367459799942208</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7402,22 +7402,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.272131314852065</v>
+        <v>0.274031314852065</v>
       </c>
       <c r="C72">
-        <v>-36.84371214042604</v>
+        <v>-39.32383693185275</v>
       </c>
       <c r="D72">
-        <v>82.20228785957399</v>
+        <v>81.51796306814727</v>
       </c>
       <c r="E72">
-        <v>124.126</v>
+        <v>125.9218</v>
       </c>
       <c r="F72">
-        <v>125.706</v>
+        <v>127.5018</v>
       </c>
       <c r="G72">
         <v>6.66</v>
@@ -7438,37 +7438,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M72">
-        <v>29.6414748</v>
+        <v>30.06492444000001</v>
       </c>
       <c r="N72">
-        <v>-22.62397480000001</v>
+        <v>-23.04742444000001</v>
       </c>
       <c r="O72">
-        <v>-5.655993700000002</v>
+        <v>-5.761856110000002</v>
       </c>
       <c r="P72">
-        <v>-16.9679811</v>
+        <v>-17.28556833</v>
       </c>
       <c r="Q72">
-        <v>-15.4479811</v>
+        <v>-15.76556833</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3894687923884218</v>
+        <v>0.4013194404018156</v>
       </c>
       <c r="T72">
-        <v>3.323539882403827</v>
+        <v>3.438144705934993</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05918649499855518</v>
+        <v>0.05835288239294173</v>
       </c>
       <c r="W72">
-        <v>0.2218438244793407</v>
+        <v>0.2220403903317443</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2367459799942208</v>
+        <v>0.2334115295717669</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7484,22 +7484,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2740313148520649</v>
+        <v>0.275931314852065</v>
       </c>
       <c r="C73">
-        <v>-39.32383693185272</v>
+        <v>-41.79266193902767</v>
       </c>
       <c r="D73">
-        <v>81.51796306814728</v>
+        <v>80.84493806097235</v>
       </c>
       <c r="E73">
-        <v>125.9218</v>
+        <v>127.7176</v>
       </c>
       <c r="F73">
-        <v>127.5018</v>
+        <v>129.2976</v>
       </c>
       <c r="G73">
         <v>6.66</v>
@@ -7520,37 +7520,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M73">
-        <v>30.06492444</v>
+        <v>30.48837408000001</v>
       </c>
       <c r="N73">
-        <v>-23.04742444</v>
+        <v>-23.47087408000001</v>
       </c>
       <c r="O73">
-        <v>-5.761856110000001</v>
+        <v>-5.867718520000002</v>
       </c>
       <c r="P73">
-        <v>-17.28556833</v>
+        <v>-17.60315556</v>
       </c>
       <c r="Q73">
-        <v>-15.76556833</v>
+        <v>-16.08315556000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4013194404018155</v>
+        <v>0.4140165632733089</v>
       </c>
       <c r="T73">
-        <v>3.438144705934992</v>
+        <v>3.560935588289813</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05835288239294174</v>
+        <v>0.05754242569303976</v>
       </c>
       <c r="W73">
-        <v>0.2220403903317443</v>
+        <v>0.2222314960215812</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2334115295717669</v>
+        <v>0.230169702772159</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7566,22 +7566,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.275931314852065</v>
+        <v>0.277831314852065</v>
       </c>
       <c r="C74">
-        <v>-41.79266193902767</v>
+        <v>-44.25046474849231</v>
       </c>
       <c r="D74">
-        <v>80.84493806097235</v>
+        <v>80.1829352515077</v>
       </c>
       <c r="E74">
-        <v>127.7176</v>
+        <v>129.5134</v>
       </c>
       <c r="F74">
-        <v>129.2976</v>
+        <v>131.0934</v>
       </c>
       <c r="G74">
         <v>6.66</v>
@@ -7602,37 +7602,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M74">
-        <v>30.48837408000001</v>
+        <v>30.91182372</v>
       </c>
       <c r="N74">
-        <v>-23.47087408000001</v>
+        <v>-23.89432372</v>
       </c>
       <c r="O74">
-        <v>-5.867718520000002</v>
+        <v>-5.973580930000001</v>
       </c>
       <c r="P74">
-        <v>-17.60315556</v>
+        <v>-17.92074279</v>
       </c>
       <c r="Q74">
-        <v>-16.08315556000001</v>
+        <v>-16.40074279</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4140165632733089</v>
+        <v>0.4276542137649129</v>
       </c>
       <c r="T74">
-        <v>3.560935588289813</v>
+        <v>3.692822091559806</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05754242569303976</v>
+        <v>0.0567541732862858</v>
       </c>
       <c r="W74">
-        <v>0.2222314960215812</v>
+        <v>0.2224173659390938</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.230169702772159</v>
+        <v>0.2270166931451432</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7648,22 +7648,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.277831314852065</v>
+        <v>0.279731314852065</v>
       </c>
       <c r="C75">
-        <v>-44.25046474849231</v>
+        <v>-46.69751392850999</v>
       </c>
       <c r="D75">
-        <v>80.1829352515077</v>
+        <v>79.53168607149003</v>
       </c>
       <c r="E75">
-        <v>129.5134</v>
+        <v>131.3092</v>
       </c>
       <c r="F75">
-        <v>131.0934</v>
+        <v>132.8892</v>
       </c>
       <c r="G75">
         <v>6.66</v>
@@ -7684,37 +7684,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M75">
-        <v>30.91182372</v>
+        <v>31.33527336000001</v>
       </c>
       <c r="N75">
-        <v>-23.89432372</v>
+        <v>-24.31777336000001</v>
       </c>
       <c r="O75">
-        <v>-5.973580930000001</v>
+        <v>-6.079443340000002</v>
       </c>
       <c r="P75">
-        <v>-17.92074279</v>
+        <v>-18.23833002000001</v>
       </c>
       <c r="Q75">
-        <v>-16.40074279</v>
+        <v>-16.71833002000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4276542137649129</v>
+        <v>0.4423409142943327</v>
       </c>
       <c r="T75">
-        <v>3.692822091559806</v>
+        <v>3.834853710465953</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0567541732862858</v>
+        <v>0.05598722499863328</v>
       </c>
       <c r="W75">
-        <v>0.2224173659390938</v>
+        <v>0.2225982123453223</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2270166931451432</v>
+        <v>0.223948899994533</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7730,22 +7730,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.279731314852065</v>
+        <v>0.281631314852065</v>
       </c>
       <c r="C76">
-        <v>-46.69751392850999</v>
+        <v>-49.13406939234913</v>
       </c>
       <c r="D76">
-        <v>79.53168607149003</v>
+        <v>78.89093060765087</v>
       </c>
       <c r="E76">
-        <v>131.3092</v>
+        <v>133.105</v>
       </c>
       <c r="F76">
-        <v>132.8892</v>
+        <v>134.685</v>
       </c>
       <c r="G76">
         <v>6.66</v>
@@ -7766,37 +7766,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M76">
-        <v>31.33527336000001</v>
+        <v>31.758723</v>
       </c>
       <c r="N76">
-        <v>-24.31777336000001</v>
+        <v>-24.74122300000001</v>
       </c>
       <c r="O76">
-        <v>-6.079443340000002</v>
+        <v>-6.185305750000001</v>
       </c>
       <c r="P76">
-        <v>-18.23833002000001</v>
+        <v>-18.55591725</v>
       </c>
       <c r="Q76">
-        <v>-16.71833002000001</v>
+        <v>-17.03591725</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4423409142943327</v>
+        <v>0.4582025508661061</v>
       </c>
       <c r="T76">
-        <v>3.834853710465953</v>
+        <v>3.988247858884591</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05598722499863328</v>
+        <v>0.05524072866531817</v>
       </c>
       <c r="W76">
-        <v>0.2225982123453223</v>
+        <v>0.222774236180718</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.223948899994533</v>
+        <v>0.2209629146612727</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7812,22 +7812,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.281631314852065</v>
+        <v>0.283531314852065</v>
       </c>
       <c r="C77">
-        <v>-49.13406939234913</v>
+        <v>-51.56038274414638</v>
       </c>
       <c r="D77">
-        <v>78.89093060765087</v>
+        <v>78.26041725585364</v>
       </c>
       <c r="E77">
-        <v>133.105</v>
+        <v>134.9008</v>
       </c>
       <c r="F77">
-        <v>134.685</v>
+        <v>136.4808</v>
       </c>
       <c r="G77">
         <v>6.66</v>
@@ -7848,37 +7848,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M77">
-        <v>31.758723</v>
+        <v>32.18217264</v>
       </c>
       <c r="N77">
-        <v>-24.74122300000001</v>
+        <v>-25.16467264000001</v>
       </c>
       <c r="O77">
-        <v>-6.185305750000001</v>
+        <v>-6.291168160000002</v>
       </c>
       <c r="P77">
-        <v>-18.55591725</v>
+        <v>-18.87350448</v>
       </c>
       <c r="Q77">
-        <v>-17.03591725</v>
+        <v>-17.35350448000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4582025508661061</v>
+        <v>0.4753859904855272</v>
       </c>
       <c r="T77">
-        <v>3.988247858884591</v>
+        <v>4.154424853004783</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05524072866531817</v>
+        <v>0.05451387697235346</v>
       </c>
       <c r="W77">
-        <v>0.222774236180718</v>
+        <v>0.2229456278099191</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2209629146612727</v>
+        <v>0.2180555078894139</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7894,22 +7894,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.283531314852065</v>
+        <v>0.285431314852065</v>
       </c>
       <c r="C78">
-        <v>-51.56038274414638</v>
+        <v>-53.97669760831556</v>
       </c>
       <c r="D78">
-        <v>78.26041725585364</v>
+        <v>77.63990239168444</v>
       </c>
       <c r="E78">
-        <v>134.9008</v>
+        <v>136.6966</v>
       </c>
       <c r="F78">
-        <v>136.4808</v>
+        <v>138.2766</v>
       </c>
       <c r="G78">
         <v>6.66</v>
@@ -7930,37 +7930,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M78">
-        <v>32.18217264</v>
+        <v>32.60562228</v>
       </c>
       <c r="N78">
-        <v>-25.16467264000001</v>
+        <v>-25.58812228</v>
       </c>
       <c r="O78">
-        <v>-6.291168160000002</v>
+        <v>-6.39703057</v>
       </c>
       <c r="P78">
-        <v>-18.87350448</v>
+        <v>-19.19109171</v>
       </c>
       <c r="Q78">
-        <v>-17.35350448000001</v>
+        <v>-17.67109171</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4753859904855272</v>
+        <v>0.4940636422457675</v>
       </c>
       <c r="T78">
-        <v>4.154424853004783</v>
+        <v>4.33505202052673</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05451387697235346</v>
+        <v>0.05380590454414109</v>
       </c>
       <c r="W78">
-        <v>0.2229456278099191</v>
+        <v>0.2231125677084915</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2180555078894139</v>
+        <v>0.2152236181765643</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7976,22 +7976,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.285431314852065</v>
+        <v>0.287331314852065</v>
       </c>
       <c r="C79">
-        <v>-53.97669760831556</v>
+        <v>-56.3832499434095</v>
       </c>
       <c r="D79">
-        <v>77.63990239168444</v>
+        <v>77.02915005659052</v>
       </c>
       <c r="E79">
-        <v>136.6966</v>
+        <v>138.4924</v>
       </c>
       <c r="F79">
-        <v>138.2766</v>
+        <v>140.0724</v>
       </c>
       <c r="G79">
         <v>6.66</v>
@@ -8012,37 +8012,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M79">
-        <v>32.60562228</v>
+        <v>33.02907192000001</v>
       </c>
       <c r="N79">
-        <v>-25.58812228</v>
+        <v>-26.01157192000001</v>
       </c>
       <c r="O79">
-        <v>-6.39703057</v>
+        <v>-6.502892980000002</v>
       </c>
       <c r="P79">
-        <v>-19.19109171</v>
+        <v>-19.50867894000001</v>
       </c>
       <c r="Q79">
-        <v>-17.67109171</v>
+        <v>-17.98867894000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4940636422457675</v>
+        <v>0.5144392623478478</v>
       </c>
       <c r="T79">
-        <v>4.33505202052673</v>
+        <v>4.532099839641581</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05380590454414109</v>
+        <v>0.05311608525511363</v>
       </c>
       <c r="W79">
-        <v>0.2231125677084915</v>
+        <v>0.2232752270968442</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2152236181765643</v>
+        <v>0.2124643410204544</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8058,22 +8058,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.287331314852065</v>
+        <v>0.289231314852065</v>
       </c>
       <c r="C80">
-        <v>-56.3832499434095</v>
+        <v>-58.78026834128271</v>
       </c>
       <c r="D80">
-        <v>77.02915005659052</v>
+        <v>76.42793165871733</v>
       </c>
       <c r="E80">
-        <v>138.4924</v>
+        <v>140.2882</v>
       </c>
       <c r="F80">
-        <v>140.0724</v>
+        <v>141.8682</v>
       </c>
       <c r="G80">
         <v>6.66</v>
@@ -8094,37 +8094,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M80">
-        <v>33.02907192000001</v>
+        <v>33.45252156000001</v>
       </c>
       <c r="N80">
-        <v>-26.01157192000001</v>
+        <v>-26.43502156000001</v>
       </c>
       <c r="O80">
-        <v>-6.502892980000002</v>
+        <v>-6.608755390000002</v>
       </c>
       <c r="P80">
-        <v>-19.50867894000001</v>
+        <v>-19.82626617000001</v>
       </c>
       <c r="Q80">
-        <v>-17.98867894000001</v>
+        <v>-18.30626617000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5144392623478478</v>
+        <v>0.5367554176977454</v>
       </c>
       <c r="T80">
-        <v>4.532099839641581</v>
+        <v>4.747914117719752</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05311608525511363</v>
+        <v>0.05244372974555522</v>
       </c>
       <c r="W80">
-        <v>0.2232752270968442</v>
+        <v>0.2234337685259981</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2124643410204544</v>
+        <v>0.2097749189822209</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8140,22 +8140,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.289231314852065</v>
+        <v>0.291131314852065</v>
       </c>
       <c r="C81">
-        <v>-58.78026834128271</v>
+        <v>-61.16797431235339</v>
       </c>
       <c r="D81">
-        <v>76.42793165871733</v>
+        <v>75.83602568764663</v>
       </c>
       <c r="E81">
-        <v>140.2882</v>
+        <v>142.084</v>
       </c>
       <c r="F81">
-        <v>141.8682</v>
+        <v>143.664</v>
       </c>
       <c r="G81">
         <v>6.66</v>
@@ -8176,37 +8176,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M81">
-        <v>33.45252156000001</v>
+        <v>33.8759712</v>
       </c>
       <c r="N81">
-        <v>-26.43502156000001</v>
+        <v>-26.8584712</v>
       </c>
       <c r="O81">
-        <v>-6.608755390000002</v>
+        <v>-6.714617800000001</v>
       </c>
       <c r="P81">
-        <v>-19.82626617000001</v>
+        <v>-20.1438534</v>
       </c>
       <c r="Q81">
-        <v>-18.30626617000001</v>
+        <v>-18.62385340000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5367554176977454</v>
+        <v>0.5613031885826326</v>
       </c>
       <c r="T81">
-        <v>4.747914117719752</v>
+        <v>4.98530982360574</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05244372974555522</v>
+        <v>0.05178818312373579</v>
       </c>
       <c r="W81">
-        <v>0.2234337685259981</v>
+        <v>0.2235883464194231</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2097749189822209</v>
+        <v>0.2071527324949431</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8222,22 +8222,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.291131314852065</v>
+        <v>0.293031314852065</v>
       </c>
       <c r="C82">
-        <v>-61.16797431235339</v>
+        <v>-63.5465825577116</v>
       </c>
       <c r="D82">
-        <v>75.83602568764663</v>
+        <v>75.25321744228843</v>
       </c>
       <c r="E82">
-        <v>142.084</v>
+        <v>143.8798</v>
       </c>
       <c r="F82">
-        <v>143.664</v>
+        <v>145.4598</v>
       </c>
       <c r="G82">
         <v>6.66</v>
@@ -8258,37 +8258,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M82">
-        <v>33.8759712</v>
+        <v>34.29942084000001</v>
       </c>
       <c r="N82">
-        <v>-26.8584712</v>
+        <v>-27.28192084000001</v>
       </c>
       <c r="O82">
-        <v>-6.714617800000001</v>
+        <v>-6.820480210000003</v>
       </c>
       <c r="P82">
-        <v>-20.1438534</v>
+        <v>-20.46144063000001</v>
       </c>
       <c r="Q82">
-        <v>-18.62385340000001</v>
+        <v>-18.94144063000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5613031885826326</v>
+        <v>0.5884349353501396</v>
       </c>
       <c r="T82">
-        <v>4.98530982360574</v>
+        <v>5.247694551163937</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05178818312373579</v>
+        <v>0.05114882283825756</v>
       </c>
       <c r="W82">
-        <v>0.2235883464194231</v>
+        <v>0.2237391075747389</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2071527324949431</v>
+        <v>0.2045952913530302</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8304,22 +8304,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.293031314852065</v>
+        <v>0.294931314852065</v>
       </c>
       <c r="C83">
-        <v>-63.5465825577116</v>
+        <v>-65.91630122877568</v>
       </c>
       <c r="D83">
-        <v>75.25321744228843</v>
+        <v>74.67929877122434</v>
       </c>
       <c r="E83">
-        <v>143.8798</v>
+        <v>145.6756</v>
       </c>
       <c r="F83">
-        <v>145.4598</v>
+        <v>147.2556</v>
       </c>
       <c r="G83">
         <v>6.66</v>
@@ -8340,37 +8340,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M83">
-        <v>34.29942084000001</v>
+        <v>34.72287048</v>
       </c>
       <c r="N83">
-        <v>-27.28192084000001</v>
+        <v>-27.70537048000001</v>
       </c>
       <c r="O83">
-        <v>-6.820480210000003</v>
+        <v>-6.926342620000002</v>
       </c>
       <c r="P83">
-        <v>-20.46144063000001</v>
+        <v>-20.77902786000001</v>
       </c>
       <c r="Q83">
-        <v>-18.94144063000001</v>
+        <v>-19.25902786000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5884349353501396</v>
+        <v>0.6185813206473696</v>
       </c>
       <c r="T83">
-        <v>5.247694551163937</v>
+        <v>5.539233137339711</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05114882283825756</v>
+        <v>0.0505250567060837</v>
       </c>
       <c r="W83">
-        <v>0.2237391075747389</v>
+        <v>0.2238861916287055</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2045952913530302</v>
+        <v>0.2021002268243347</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8386,22 +8386,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.294931314852065</v>
+        <v>0.296831314852065</v>
       </c>
       <c r="C84">
-        <v>-65.91630122877568</v>
+        <v>-68.27733217515758</v>
       </c>
       <c r="D84">
-        <v>74.67929877122434</v>
+        <v>74.11406782484245</v>
       </c>
       <c r="E84">
-        <v>145.6756</v>
+        <v>147.4714</v>
       </c>
       <c r="F84">
-        <v>147.2556</v>
+        <v>149.0514</v>
       </c>
       <c r="G84">
         <v>6.66</v>
@@ -8422,37 +8422,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M84">
-        <v>34.72287048</v>
+        <v>35.14632012000001</v>
       </c>
       <c r="N84">
-        <v>-27.70537048000001</v>
+        <v>-28.12882012000001</v>
       </c>
       <c r="O84">
-        <v>-6.926342620000002</v>
+        <v>-7.032205030000002</v>
       </c>
       <c r="P84">
-        <v>-20.77902786000001</v>
+        <v>-21.09661509000001</v>
       </c>
       <c r="Q84">
-        <v>-19.25902786000001</v>
+        <v>-19.57661509000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6185813206473696</v>
+        <v>0.6522743395089797</v>
       </c>
       <c r="T84">
-        <v>5.539233137339711</v>
+        <v>5.865070380712637</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0505250567060837</v>
+        <v>0.04991632108311883</v>
       </c>
       <c r="W84">
-        <v>0.2238861916287055</v>
+        <v>0.2240297314886006</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2021002268243347</v>
+        <v>0.1996652843324753</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8468,22 +8468,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.296831314852065</v>
+        <v>0.298731314852065</v>
       </c>
       <c r="C85">
-        <v>-68.27733217515758</v>
+        <v>-70.62987118135601</v>
       </c>
       <c r="D85">
-        <v>74.11406782484245</v>
+        <v>73.55732881864401</v>
       </c>
       <c r="E85">
-        <v>147.4714</v>
+        <v>149.2672</v>
       </c>
       <c r="F85">
-        <v>149.0514</v>
+        <v>150.8472</v>
       </c>
       <c r="G85">
         <v>6.66</v>
@@ -8504,37 +8504,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M85">
-        <v>35.14632012000001</v>
+        <v>35.56976976000001</v>
       </c>
       <c r="N85">
-        <v>-28.12882012000001</v>
+        <v>-28.55226976000001</v>
       </c>
       <c r="O85">
-        <v>-7.032205030000002</v>
+        <v>-7.138067440000002</v>
       </c>
       <c r="P85">
-        <v>-21.09661509000001</v>
+        <v>-21.41420232000001</v>
       </c>
       <c r="Q85">
-        <v>-19.57661509000001</v>
+        <v>-19.89420232000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6522743395089797</v>
+        <v>0.6901789857282911</v>
       </c>
       <c r="T85">
-        <v>5.865070380712637</v>
+        <v>6.231637279507177</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04991632108311883</v>
+        <v>0.04932207916546265</v>
       </c>
       <c r="W85">
-        <v>0.2240297314886006</v>
+        <v>0.2241698537327839</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1996652843324753</v>
+        <v>0.1972883166618505</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8550,22 +8550,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.298731314852065</v>
+        <v>0.300631314852065</v>
       </c>
       <c r="C86">
-        <v>-70.62987118135601</v>
+        <v>-72.97410819286125</v>
       </c>
       <c r="D86">
-        <v>73.55732881864401</v>
+        <v>73.00889180713875</v>
       </c>
       <c r="E86">
-        <v>149.2672</v>
+        <v>151.063</v>
       </c>
       <c r="F86">
-        <v>150.8472</v>
+        <v>152.643</v>
       </c>
       <c r="G86">
         <v>6.66</v>
@@ -8586,37 +8586,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M86">
-        <v>35.56976976000001</v>
+        <v>35.9932194</v>
       </c>
       <c r="N86">
-        <v>-28.55226976000001</v>
+        <v>-28.9757194</v>
       </c>
       <c r="O86">
-        <v>-7.138067440000002</v>
+        <v>-7.243929850000001</v>
       </c>
       <c r="P86">
-        <v>-21.41420232000001</v>
+        <v>-21.73178955</v>
       </c>
       <c r="Q86">
-        <v>-19.89420232000001</v>
+        <v>-20.21178955</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6901789857282906</v>
+        <v>0.7331375847768432</v>
       </c>
       <c r="T86">
-        <v>6.231637279507173</v>
+        <v>6.647079764807651</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04932207916546265</v>
+        <v>0.04874181941057486</v>
       </c>
       <c r="W86">
-        <v>0.2241698537327839</v>
+        <v>0.2243066789829865</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1972883166618505</v>
+        <v>0.1949672776422994</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8632,22 +8632,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.300631314852065</v>
+        <v>0.302531314852065</v>
       </c>
       <c r="C87">
-        <v>-72.97410819286125</v>
+        <v>-75.31022753221998</v>
       </c>
       <c r="D87">
-        <v>73.00889180713875</v>
+        <v>72.46857246778004</v>
       </c>
       <c r="E87">
-        <v>151.063</v>
+        <v>152.8588</v>
       </c>
       <c r="F87">
-        <v>152.643</v>
+        <v>154.4388</v>
       </c>
       <c r="G87">
         <v>6.66</v>
@@ -8668,37 +8668,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M87">
-        <v>35.9932194</v>
+        <v>36.41666904</v>
       </c>
       <c r="N87">
-        <v>-28.9757194</v>
+        <v>-29.39916904</v>
       </c>
       <c r="O87">
-        <v>-7.243929850000001</v>
+        <v>-7.349792260000001</v>
       </c>
       <c r="P87">
-        <v>-21.73178955</v>
+        <v>-22.04937678</v>
       </c>
       <c r="Q87">
-        <v>-20.21178955</v>
+        <v>-20.52937678</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7331375847768432</v>
+        <v>0.7822331265466178</v>
       </c>
       <c r="T87">
-        <v>6.647079764807651</v>
+        <v>7.121871176579626</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04874181941057486</v>
+        <v>0.04817505406859143</v>
       </c>
       <c r="W87">
-        <v>0.2243066789829865</v>
+        <v>0.2244403222506262</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1949672776422994</v>
+        <v>0.1927002162743657</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8714,22 +8714,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.302531314852065</v>
+        <v>0.304431314852065</v>
       </c>
       <c r="C88">
-        <v>-75.31022753221998</v>
+        <v>-77.63840810557606</v>
       </c>
       <c r="D88">
-        <v>72.46857246778004</v>
+        <v>71.93619189442394</v>
       </c>
       <c r="E88">
-        <v>152.8588</v>
+        <v>154.6546</v>
       </c>
       <c r="F88">
-        <v>154.4388</v>
+        <v>156.2346</v>
       </c>
       <c r="G88">
         <v>6.66</v>
@@ -8750,37 +8750,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M88">
-        <v>36.41666904</v>
+        <v>36.84011868</v>
       </c>
       <c r="N88">
-        <v>-29.39916904</v>
+        <v>-29.82261868000001</v>
       </c>
       <c r="O88">
-        <v>-7.349792260000001</v>
+        <v>-7.455654670000001</v>
       </c>
       <c r="P88">
-        <v>-22.04937678</v>
+        <v>-22.36696401</v>
       </c>
       <c r="Q88">
-        <v>-20.52937678</v>
+        <v>-20.84696401</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7822331265466178</v>
+        <v>0.8388818285886653</v>
       </c>
       <c r="T88">
-        <v>7.121871176579626</v>
+        <v>7.669707420931905</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04817505406859143</v>
+        <v>0.04762131781492946</v>
       </c>
       <c r="W88">
-        <v>0.2244403222506262</v>
+        <v>0.2245708932592396</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1927002162743657</v>
+        <v>0.1904852712597178</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8796,22 +8796,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.304431314852065</v>
+        <v>0.3063313148520649</v>
       </c>
       <c r="C89">
-        <v>-77.63840810557606</v>
+        <v>-79.95882360017416</v>
       </c>
       <c r="D89">
-        <v>71.93619189442394</v>
+        <v>71.41157639982586</v>
       </c>
       <c r="E89">
-        <v>154.6546</v>
+        <v>156.4504</v>
       </c>
       <c r="F89">
-        <v>156.2346</v>
+        <v>158.0304</v>
       </c>
       <c r="G89">
         <v>6.66</v>
@@ -8832,37 +8832,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M89">
-        <v>36.84011868</v>
+        <v>37.26356832</v>
       </c>
       <c r="N89">
-        <v>-29.82261868000001</v>
+        <v>-30.24606832000001</v>
       </c>
       <c r="O89">
-        <v>-7.455654670000001</v>
+        <v>-7.561517080000002</v>
       </c>
       <c r="P89">
-        <v>-22.36696401</v>
+        <v>-22.68455124</v>
       </c>
       <c r="Q89">
-        <v>-20.84696401</v>
+        <v>-21.16455124000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8388818285886653</v>
+        <v>0.9049719809710541</v>
       </c>
       <c r="T89">
-        <v>7.669707420931905</v>
+        <v>8.308849706009564</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04762131781492946</v>
+        <v>0.04708016647612345</v>
       </c>
       <c r="W89">
-        <v>0.2245708932592396</v>
+        <v>0.2246984967449301</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1904852712597178</v>
+        <v>0.1883206659044937</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8878,22 +8878,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3063313148520649</v>
+        <v>0.308231314852065</v>
       </c>
       <c r="C90">
-        <v>-79.95882360017416</v>
+        <v>-82.27164267328344</v>
       </c>
       <c r="D90">
-        <v>71.41157639982586</v>
+        <v>70.89455732671657</v>
       </c>
       <c r="E90">
-        <v>156.4504</v>
+        <v>158.2462</v>
       </c>
       <c r="F90">
-        <v>158.0304</v>
+        <v>159.8262</v>
       </c>
       <c r="G90">
         <v>6.66</v>
@@ -8914,37 +8914,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M90">
-        <v>37.26356832</v>
+        <v>37.68701796</v>
       </c>
       <c r="N90">
-        <v>-30.24606832000001</v>
+        <v>-30.66951796</v>
       </c>
       <c r="O90">
-        <v>-7.561517080000002</v>
+        <v>-7.66737949</v>
       </c>
       <c r="P90">
-        <v>-22.68455124</v>
+        <v>-23.00213847</v>
       </c>
       <c r="Q90">
-        <v>-21.16455124000001</v>
+        <v>-21.48213847</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.9049719809710541</v>
+        <v>0.9830785246956955</v>
       </c>
       <c r="T90">
-        <v>8.308849706009564</v>
+        <v>9.064199679283162</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04708016647612345</v>
+        <v>0.04655117584156027</v>
       </c>
       <c r="W90">
-        <v>0.2246984967449301</v>
+        <v>0.2248232327365601</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1883206659044937</v>
+        <v>0.1862047033662411</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8960,22 +8960,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.308231314852065</v>
+        <v>0.310131314852065</v>
       </c>
       <c r="C91">
-        <v>-82.27164267328344</v>
+        <v>-84.57702913297382</v>
       </c>
       <c r="D91">
-        <v>70.89455732671657</v>
+        <v>70.3849708670262</v>
       </c>
       <c r="E91">
-        <v>158.2462</v>
+        <v>160.042</v>
       </c>
       <c r="F91">
-        <v>159.8262</v>
+        <v>161.622</v>
       </c>
       <c r="G91">
         <v>6.66</v>
@@ -8996,37 +8996,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M91">
-        <v>37.68701796</v>
+        <v>38.11046760000001</v>
       </c>
       <c r="N91">
-        <v>-30.66951796</v>
+        <v>-31.09296760000001</v>
       </c>
       <c r="O91">
-        <v>-7.66737949</v>
+        <v>-7.773241900000002</v>
       </c>
       <c r="P91">
-        <v>-23.00213847</v>
+        <v>-23.31972570000001</v>
       </c>
       <c r="Q91">
-        <v>-21.48213847</v>
+        <v>-21.79972570000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9830785246956955</v>
+        <v>1.076806377165265</v>
       </c>
       <c r="T91">
-        <v>9.064199679283162</v>
+        <v>9.97061964721148</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04655117584156027</v>
+        <v>0.04603394055443181</v>
       </c>
       <c r="W91">
-        <v>0.2248232327365601</v>
+        <v>0.224945196817265</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1862047033662411</v>
+        <v>0.1841357622177272</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9042,22 +9042,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.310131314852065</v>
+        <v>0.312031314852065</v>
       </c>
       <c r="C92">
-        <v>-84.57702913297382</v>
+        <v>-86.87514211115094</v>
       </c>
       <c r="D92">
-        <v>70.3849708670262</v>
+        <v>69.8826578888491</v>
       </c>
       <c r="E92">
-        <v>160.042</v>
+        <v>161.8378</v>
       </c>
       <c r="F92">
-        <v>161.622</v>
+        <v>163.4178</v>
       </c>
       <c r="G92">
         <v>6.66</v>
@@ -9078,37 +9078,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M92">
-        <v>38.11046760000001</v>
+        <v>38.53391724000001</v>
       </c>
       <c r="N92">
-        <v>-31.09296760000001</v>
+        <v>-31.51641724000001</v>
       </c>
       <c r="O92">
-        <v>-7.773241900000002</v>
+        <v>-7.879104310000002</v>
       </c>
       <c r="P92">
-        <v>-23.31972570000001</v>
+        <v>-23.63731293000001</v>
       </c>
       <c r="Q92">
-        <v>-21.79972570000001</v>
+        <v>-22.11731293000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.076806377165265</v>
+        <v>1.191362641294739</v>
       </c>
       <c r="T92">
-        <v>9.97061964721148</v>
+        <v>11.07846627467942</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04603394055443181</v>
+        <v>0.04552807307581168</v>
       </c>
       <c r="W92">
-        <v>0.224945196817265</v>
+        <v>0.2250644803687236</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1841357622177272</v>
+        <v>0.1821122923032467</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9124,22 +9124,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.312031314852065</v>
+        <v>0.313931314852065</v>
       </c>
       <c r="C93">
-        <v>-86.87514211115094</v>
+        <v>-89.16613622923474</v>
       </c>
       <c r="D93">
-        <v>69.8826578888491</v>
+        <v>69.38746377076528</v>
       </c>
       <c r="E93">
-        <v>161.8378</v>
+        <v>163.6336</v>
       </c>
       <c r="F93">
-        <v>163.4178</v>
+        <v>165.2136</v>
       </c>
       <c r="G93">
         <v>6.66</v>
@@ -9160,37 +9160,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M93">
-        <v>38.53391724000001</v>
+        <v>38.95736688</v>
       </c>
       <c r="N93">
-        <v>-31.51641724000001</v>
+        <v>-31.93986688</v>
       </c>
       <c r="O93">
-        <v>-7.879104310000002</v>
+        <v>-7.984966720000001</v>
       </c>
       <c r="P93">
-        <v>-23.63731293000001</v>
+        <v>-23.95490016</v>
       </c>
       <c r="Q93">
-        <v>-22.11731293000001</v>
+        <v>-22.43490016</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.191362641294739</v>
+        <v>1.334557971456582</v>
       </c>
       <c r="T93">
-        <v>11.07846627467942</v>
+        <v>12.46327455901435</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04552807307581168</v>
+        <v>0.04503320271629199</v>
       </c>
       <c r="W93">
-        <v>0.2250644803687236</v>
+        <v>0.2251811707994984</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1821122923032467</v>
+        <v>0.180132810865168</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9206,22 +9206,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.313931314852065</v>
+        <v>0.3158313148520651</v>
       </c>
       <c r="C94">
-        <v>-89.16613622923474</v>
+        <v>-91.45016175684322</v>
       </c>
       <c r="D94">
-        <v>69.38746377076528</v>
+        <v>68.89923824315682</v>
       </c>
       <c r="E94">
-        <v>163.6336</v>
+        <v>165.4294</v>
       </c>
       <c r="F94">
-        <v>165.2136</v>
+        <v>167.0094</v>
       </c>
       <c r="G94">
         <v>6.66</v>
@@ -9242,37 +9242,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M94">
-        <v>38.95736688</v>
+        <v>39.38081652000001</v>
       </c>
       <c r="N94">
-        <v>-31.93986688</v>
+        <v>-32.36331652000001</v>
       </c>
       <c r="O94">
-        <v>-7.984966720000001</v>
+        <v>-8.090829130000003</v>
       </c>
       <c r="P94">
-        <v>-23.95490016</v>
+        <v>-24.27248739000001</v>
       </c>
       <c r="Q94">
-        <v>-22.43490016</v>
+        <v>-22.75248739000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.334557971456582</v>
+        <v>1.518666253093237</v>
       </c>
       <c r="T94">
-        <v>12.46327455901435</v>
+        <v>14.24374235315926</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04503320271629199</v>
+        <v>0.04454897473009529</v>
       </c>
       <c r="W94">
-        <v>0.2251811707994984</v>
+        <v>0.2252953517586435</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.180132810865168</v>
+        <v>0.1781958989203811</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9288,22 +9288,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3158313148520651</v>
+        <v>0.317731314852065</v>
       </c>
       <c r="C95">
-        <v>-91.45016175684322</v>
+        <v>-93.72736476382386</v>
       </c>
       <c r="D95">
-        <v>68.89923824315682</v>
+        <v>68.41783523617616</v>
       </c>
       <c r="E95">
-        <v>165.4294</v>
+        <v>167.2252</v>
       </c>
       <c r="F95">
-        <v>167.0094</v>
+        <v>168.8052</v>
       </c>
       <c r="G95">
         <v>6.66</v>
@@ -9324,37 +9324,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M95">
-        <v>39.38081652000001</v>
+        <v>39.80426616</v>
       </c>
       <c r="N95">
-        <v>-32.36331652000001</v>
+        <v>-32.78676616000001</v>
       </c>
       <c r="O95">
-        <v>-8.090829130000003</v>
+        <v>-8.196691540000002</v>
       </c>
       <c r="P95">
-        <v>-24.27248739000001</v>
+        <v>-24.59007462</v>
       </c>
       <c r="Q95">
-        <v>-22.75248739000001</v>
+        <v>-23.07007462</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.518666253093237</v>
+        <v>1.76414396194211</v>
       </c>
       <c r="T95">
-        <v>14.24374235315926</v>
+        <v>16.61769941201915</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04454897473009529</v>
+        <v>0.04407504946700918</v>
       </c>
       <c r="W95">
-        <v>0.2252953517586435</v>
+        <v>0.2254071033356793</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1781958989203811</v>
+        <v>0.1763001978680367</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9370,22 +9370,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.317731314852065</v>
+        <v>0.319631314852065</v>
       </c>
       <c r="C96">
-        <v>-93.72736476382386</v>
+        <v>-95.99788726595614</v>
       </c>
       <c r="D96">
-        <v>68.41783523617616</v>
+        <v>67.94311273404389</v>
       </c>
       <c r="E96">
-        <v>167.2252</v>
+        <v>169.021</v>
       </c>
       <c r="F96">
-        <v>168.8052</v>
+        <v>170.601</v>
       </c>
       <c r="G96">
         <v>6.66</v>
@@ -9406,37 +9406,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M96">
-        <v>39.80426616</v>
+        <v>40.22771580000001</v>
       </c>
       <c r="N96">
-        <v>-32.78676616000001</v>
+        <v>-33.21021580000001</v>
       </c>
       <c r="O96">
-        <v>-8.196691540000002</v>
+        <v>-8.302553950000002</v>
       </c>
       <c r="P96">
-        <v>-24.59007462</v>
+        <v>-24.90766185</v>
       </c>
       <c r="Q96">
-        <v>-23.07007462</v>
+        <v>-23.38766185</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.76414396194211</v>
+        <v>2.107812754330533</v>
       </c>
       <c r="T96">
-        <v>16.61769941201915</v>
+        <v>19.94123929442298</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04407504946700918</v>
+        <v>0.04361110157788277</v>
       </c>
       <c r="W96">
-        <v>0.2254071033356793</v>
+        <v>0.2255165022479353</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1763001978680367</v>
+        <v>0.174444406311531</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9452,22 +9452,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.319631314852065</v>
+        <v>0.321531314852065</v>
       </c>
       <c r="C97">
-        <v>-95.99788726595614</v>
+        <v>-98.26186736462914</v>
       </c>
       <c r="D97">
-        <v>67.94311273404389</v>
+        <v>67.47493263537088</v>
       </c>
       <c r="E97">
-        <v>169.021</v>
+        <v>170.8168</v>
       </c>
       <c r="F97">
-        <v>170.601</v>
+        <v>172.3968</v>
       </c>
       <c r="G97">
         <v>6.66</v>
@@ -9488,37 +9488,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M97">
-        <v>40.22771580000001</v>
+        <v>40.65116544000001</v>
       </c>
       <c r="N97">
-        <v>-33.21021580000001</v>
+        <v>-33.63366544000001</v>
       </c>
       <c r="O97">
-        <v>-8.302553950000002</v>
+        <v>-8.408416360000002</v>
       </c>
       <c r="P97">
-        <v>-24.90766185</v>
+        <v>-25.22524908</v>
       </c>
       <c r="Q97">
-        <v>-23.38766185</v>
+        <v>-23.70524908000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.107812754330533</v>
+        <v>2.623315942913167</v>
       </c>
       <c r="T97">
-        <v>19.94123929442298</v>
+        <v>24.92654911802874</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04361110157788277</v>
+        <v>0.04315681926977982</v>
       </c>
       <c r="W97">
-        <v>0.2255165022479353</v>
+        <v>0.2256236220161859</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.174444406311531</v>
+        <v>0.1726272770791193</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9534,22 +9534,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.321531314852065</v>
+        <v>0.323431314852065</v>
       </c>
       <c r="C98">
-        <v>-98.26186736462914</v>
+        <v>-100.5194393807848</v>
       </c>
       <c r="D98">
-        <v>67.47493263537088</v>
+        <v>67.01316061921516</v>
       </c>
       <c r="E98">
-        <v>170.8168</v>
+        <v>172.6126</v>
       </c>
       <c r="F98">
-        <v>172.3968</v>
+        <v>174.1926</v>
       </c>
       <c r="G98">
         <v>6.66</v>
@@ -9570,37 +9570,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M98">
-        <v>40.65116544000001</v>
+        <v>41.07461508</v>
       </c>
       <c r="N98">
-        <v>-33.63366544000001</v>
+        <v>-34.05711508</v>
       </c>
       <c r="O98">
-        <v>-8.408416360000002</v>
+        <v>-8.514278770000001</v>
       </c>
       <c r="P98">
-        <v>-25.22524908</v>
+        <v>-25.54283631</v>
       </c>
       <c r="Q98">
-        <v>-23.70524908000001</v>
+        <v>-24.02283631</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.62331594291316</v>
+        <v>3.482487923884214</v>
       </c>
       <c r="T98">
-        <v>24.92654911802867</v>
+        <v>33.23539882403823</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04315681926977982</v>
+        <v>0.04271190360720478</v>
       </c>
       <c r="W98">
-        <v>0.2256236220161859</v>
+        <v>0.2257285331294211</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1726272770791193</v>
+        <v>0.1708476144288191</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9616,22 +9616,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.323431314852065</v>
+        <v>0.325331314852065</v>
       </c>
       <c r="C99">
-        <v>-100.5194393807848</v>
+        <v>-102.7707339833982</v>
       </c>
       <c r="D99">
-        <v>67.01316061921516</v>
+        <v>66.55766601660186</v>
       </c>
       <c r="E99">
-        <v>172.6126</v>
+        <v>174.4084</v>
       </c>
       <c r="F99">
-        <v>174.1926</v>
+        <v>175.9884</v>
       </c>
       <c r="G99">
         <v>6.66</v>
@@ -9652,37 +9652,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M99">
-        <v>41.07461508</v>
+        <v>41.49806472</v>
       </c>
       <c r="N99">
-        <v>-34.05711508</v>
+        <v>-34.48056472</v>
       </c>
       <c r="O99">
-        <v>-8.514278770000001</v>
+        <v>-8.620141180000001</v>
       </c>
       <c r="P99">
-        <v>-25.54283631</v>
+        <v>-25.86042354</v>
       </c>
       <c r="Q99">
-        <v>-24.02283631</v>
+        <v>-24.34042354</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.482487923884214</v>
+        <v>5.200831885826321</v>
       </c>
       <c r="T99">
-        <v>33.23539882403823</v>
+        <v>49.85309823605735</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04271190360720478</v>
+        <v>0.04227606785611085</v>
       </c>
       <c r="W99">
-        <v>0.2257285331294211</v>
+        <v>0.2258313031995291</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1708476144288191</v>
+        <v>0.1691042714244434</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9698,22 +9698,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.325331314852065</v>
+        <v>0.327231314852065</v>
       </c>
       <c r="C100">
-        <v>-102.7707339833982</v>
+        <v>-105.0158783127526</v>
       </c>
       <c r="D100">
-        <v>66.55766601660186</v>
+        <v>66.1083216872474</v>
       </c>
       <c r="E100">
-        <v>174.4084</v>
+        <v>176.2042</v>
       </c>
       <c r="F100">
-        <v>175.9884</v>
+        <v>177.7842</v>
       </c>
       <c r="G100">
         <v>6.66</v>
@@ -9734,37 +9734,37 @@
         <v>7.017499999999999</v>
       </c>
       <c r="M100">
-        <v>41.49806472</v>
+        <v>41.92151436</v>
       </c>
       <c r="N100">
-        <v>-34.48056472</v>
+        <v>-34.90401436000001</v>
       </c>
       <c r="O100">
-        <v>-8.620141180000001</v>
+        <v>-8.726003590000001</v>
       </c>
       <c r="P100">
-        <v>-25.86042354</v>
+        <v>-26.17801077</v>
       </c>
       <c r="Q100">
-        <v>-24.34042354</v>
+        <v>-24.65801077</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.200831885826321</v>
+        <v>10.35586377165264</v>
       </c>
       <c r="T100">
-        <v>49.85309823605735</v>
+        <v>99.7061964721147</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04227606785611085</v>
+        <v>0.04184903686766529</v>
       </c>
       <c r="W100">
-        <v>0.2258313031995291</v>
+        <v>0.2259319971066045</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9772,91 +9772,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1691042714244434</v>
+        <v>0.1673961474706611</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.327231314852065</v>
-      </c>
-      <c r="C101">
-        <v>-105.0158783127526</v>
-      </c>
-      <c r="D101">
-        <v>66.1083216872474</v>
-      </c>
-      <c r="E101">
-        <v>176.2042</v>
-      </c>
-      <c r="F101">
-        <v>177.7842</v>
-      </c>
-      <c r="G101">
-        <v>6.66</v>
-      </c>
-      <c r="H101">
-        <v>178</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>8.5375</v>
-      </c>
-      <c r="K101">
-        <v>1.52</v>
-      </c>
-      <c r="L101">
-        <v>7.017499999999999</v>
-      </c>
-      <c r="M101">
-        <v>41.92151436</v>
-      </c>
-      <c r="N101">
-        <v>-34.90401436000001</v>
-      </c>
-      <c r="O101">
-        <v>-8.726003590000001</v>
-      </c>
-      <c r="P101">
-        <v>-26.17801077</v>
-      </c>
-      <c r="Q101">
-        <v>-24.65801077</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>10.35586377165264</v>
-      </c>
-      <c r="T101">
-        <v>99.7061964721147</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04184903686766529</v>
-      </c>
-      <c r="W101">
-        <v>0.2259319971066045</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1673961474706611</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
